--- a/research/traditional_assets/database/data/romania/romania_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_oil_gas_integrated.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1137183940620466</v>
+        <v>0.1135742446315473</v>
       </c>
       <c r="C2">
-        <v>9388.494153197827</v>
+        <v>9304.605722409617</v>
       </c>
       <c r="D2">
-        <v>6918.094153197827</v>
+        <v>6928.020722409617</v>
       </c>
       <c r="E2">
-        <v>-186.2</v>
+        <v>-92.38499999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>93.815</v>
       </c>
       <c r="G2">
         <v>2470.4</v>
@@ -1451,28 +1451,28 @@
         <v>1333.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.718894499999999</v>
       </c>
       <c r="N2">
-        <v>1333.8</v>
+        <v>1329.0811055</v>
       </c>
       <c r="O2">
-        <v>213.408</v>
+        <v>212.65297688</v>
       </c>
       <c r="P2">
-        <v>1120.392</v>
+        <v>1116.42812862</v>
       </c>
       <c r="Q2">
-        <v>1900.992</v>
+        <v>1897.02812862</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1137183940620466</v>
+        <v>0.1142946713449973</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9428549327994783</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>282.6509471656975</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1135742446315473</v>
+        <v>0.1134300952010481</v>
       </c>
       <c r="C3">
-        <v>9304.605722409617</v>
+        <v>9220.745819237485</v>
       </c>
       <c r="D3">
-        <v>6928.020722409617</v>
+        <v>6937.975819237484</v>
       </c>
       <c r="E3">
-        <v>-92.38499999999999</v>
+        <v>1.430000000000007</v>
       </c>
       <c r="F3">
-        <v>93.815</v>
+        <v>187.63</v>
       </c>
       <c r="G3">
         <v>2470.4</v>
@@ -1533,28 +1533,28 @@
         <v>1333.8</v>
       </c>
       <c r="M3">
-        <v>4.718894499999999</v>
+        <v>9.437788999999999</v>
       </c>
       <c r="N3">
-        <v>1329.0811055</v>
+        <v>1324.362211</v>
       </c>
       <c r="O3">
-        <v>212.65297688</v>
+        <v>211.89795376</v>
       </c>
       <c r="P3">
-        <v>1116.42812862</v>
+        <v>1112.46425724</v>
       </c>
       <c r="Q3">
-        <v>1897.02812862</v>
+        <v>1893.06425724</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1142946713449973</v>
+        <v>0.1148827093888246</v>
       </c>
       <c r="T3">
-        <v>0.9428549327994783</v>
+        <v>0.95094949781321</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>282.6509471656975</v>
+        <v>141.3254735828487</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1134300952010481</v>
+        <v>0.1132859457705488</v>
       </c>
       <c r="C4">
-        <v>9220.745819237485</v>
+        <v>9136.914566835152</v>
       </c>
       <c r="D4">
-        <v>6937.975819237484</v>
+        <v>6947.959566835151</v>
       </c>
       <c r="E4">
-        <v>1.430000000000007</v>
+        <v>95.245</v>
       </c>
       <c r="F4">
-        <v>187.63</v>
+        <v>281.445</v>
       </c>
       <c r="G4">
         <v>2470.4</v>
@@ -1615,28 +1615,28 @@
         <v>1333.8</v>
       </c>
       <c r="M4">
-        <v>9.437788999999999</v>
+        <v>14.1566835</v>
       </c>
       <c r="N4">
-        <v>1324.362211</v>
+        <v>1319.6433165</v>
       </c>
       <c r="O4">
-        <v>211.89795376</v>
+        <v>211.14293064</v>
       </c>
       <c r="P4">
-        <v>1112.46425724</v>
+        <v>1108.50038586</v>
       </c>
       <c r="Q4">
-        <v>1893.06425724</v>
+        <v>1889.10038586</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1148827093888246</v>
+        <v>0.1154828719284008</v>
       </c>
       <c r="T4">
-        <v>0.95094949781321</v>
+        <v>0.9592109610746477</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>141.3254735828487</v>
+        <v>94.21698238856581</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1132859457705488</v>
+        <v>0.1131417963400495</v>
       </c>
       <c r="C5">
-        <v>9136.914566835152</v>
+        <v>9053.112089066237</v>
       </c>
       <c r="D5">
-        <v>6947.959566835151</v>
+        <v>6957.972089066237</v>
       </c>
       <c r="E5">
-        <v>95.245</v>
+        <v>189.06</v>
       </c>
       <c r="F5">
-        <v>281.445</v>
+        <v>375.26</v>
       </c>
       <c r="G5">
         <v>2470.4</v>
@@ -1697,28 +1697,28 @@
         <v>1333.8</v>
       </c>
       <c r="M5">
-        <v>14.1566835</v>
+        <v>18.875578</v>
       </c>
       <c r="N5">
-        <v>1319.6433165</v>
+        <v>1314.924422</v>
       </c>
       <c r="O5">
-        <v>211.14293064</v>
+        <v>210.3879075200001</v>
       </c>
       <c r="P5">
-        <v>1108.50038586</v>
+        <v>1104.53651448</v>
       </c>
       <c r="Q5">
-        <v>1889.10038586</v>
+        <v>1885.13651448</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1154828719284008</v>
+        <v>0.1160955378542183</v>
       </c>
       <c r="T5">
-        <v>0.9592109610746477</v>
+        <v>0.9676445381540317</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>94.21698238856581</v>
+        <v>70.66273679142436</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1131417963400495</v>
+        <v>0.1129976469095502</v>
       </c>
       <c r="C6">
-        <v>9053.112089066237</v>
+        <v>8969.338510509375</v>
       </c>
       <c r="D6">
-        <v>6957.972089066237</v>
+        <v>6968.013510509376</v>
       </c>
       <c r="E6">
-        <v>189.06</v>
+        <v>282.8750000000001</v>
       </c>
       <c r="F6">
-        <v>375.26</v>
+        <v>469.075</v>
       </c>
       <c r="G6">
         <v>2470.4</v>
@@ -1779,28 +1779,28 @@
         <v>1333.8</v>
       </c>
       <c r="M6">
-        <v>18.875578</v>
+        <v>23.5944725</v>
       </c>
       <c r="N6">
-        <v>1314.924422</v>
+        <v>1310.2055275</v>
       </c>
       <c r="O6">
-        <v>210.3879075200001</v>
+        <v>209.6328844000001</v>
       </c>
       <c r="P6">
-        <v>1104.53651448</v>
+        <v>1100.5726431</v>
       </c>
       <c r="Q6">
-        <v>1885.13651448</v>
+        <v>1881.1726431</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1160955378542183</v>
+        <v>0.1167211020100529</v>
       </c>
       <c r="T6">
-        <v>0.9676445381540317</v>
+        <v>0.976255664224561</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>70.66273679142436</v>
+        <v>56.53018943313948</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1129976469095502</v>
+        <v>0.112853497479051</v>
       </c>
       <c r="C7">
-        <v>8969.338510509375</v>
+        <v>8885.593956463388</v>
       </c>
       <c r="D7">
-        <v>6968.013510509376</v>
+        <v>6978.083956463387</v>
       </c>
       <c r="E7">
-        <v>282.8750000000001</v>
+        <v>376.6900000000001</v>
       </c>
       <c r="F7">
-        <v>469.075</v>
+        <v>562.8900000000001</v>
       </c>
       <c r="G7">
         <v>2470.4</v>
@@ -1861,28 +1861,28 @@
         <v>1333.8</v>
       </c>
       <c r="M7">
-        <v>23.5944725</v>
+        <v>28.313367</v>
       </c>
       <c r="N7">
-        <v>1310.2055275</v>
+        <v>1305.486633</v>
       </c>
       <c r="O7">
-        <v>209.6328844000001</v>
+        <v>208.87786128</v>
       </c>
       <c r="P7">
-        <v>1100.5726431</v>
+        <v>1096.60877172</v>
       </c>
       <c r="Q7">
-        <v>1881.1726431</v>
+        <v>1877.20877172</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1167211020100529</v>
+        <v>0.1173599760415436</v>
       </c>
       <c r="T7">
-        <v>0.976255664224561</v>
+        <v>0.9850500057433994</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>56.53018943313948</v>
+        <v>47.1084911942829</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.112853497479051</v>
+        <v>0.1127093480485517</v>
       </c>
       <c r="C8">
-        <v>8885.593956463388</v>
+        <v>8801.878552952483</v>
       </c>
       <c r="D8">
-        <v>6978.083956463387</v>
+        <v>6988.183552952482</v>
       </c>
       <c r="E8">
-        <v>376.69</v>
+        <v>470.5049999999999</v>
       </c>
       <c r="F8">
-        <v>562.89</v>
+        <v>656.7049999999999</v>
       </c>
       <c r="G8">
         <v>2470.4</v>
@@ -1943,28 +1943,28 @@
         <v>1333.8</v>
       </c>
       <c r="M8">
-        <v>28.313367</v>
+        <v>33.0322615</v>
       </c>
       <c r="N8">
-        <v>1305.486633</v>
+        <v>1300.7677385</v>
       </c>
       <c r="O8">
-        <v>208.87786128</v>
+        <v>208.12283816</v>
       </c>
       <c r="P8">
-        <v>1096.60877172</v>
+        <v>1092.64490034</v>
       </c>
       <c r="Q8">
-        <v>1877.20877172</v>
+        <v>1873.24490034</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1173599760415436</v>
+        <v>0.118012589299518</v>
       </c>
       <c r="T8">
-        <v>0.9850500057433994</v>
+        <v>0.9940334728862986</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.10849119428291</v>
+        <v>40.37870673795678</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1127093480485517</v>
+        <v>0.1125651986180524</v>
       </c>
       <c r="C9">
-        <v>8801.878552952483</v>
+        <v>8718.192426731532</v>
       </c>
       <c r="D9">
-        <v>6988.183552952483</v>
+        <v>6998.312426731532</v>
       </c>
       <c r="E9">
-        <v>470.5050000000001</v>
+        <v>564.3199999999999</v>
       </c>
       <c r="F9">
-        <v>656.705</v>
+        <v>750.52</v>
       </c>
       <c r="G9">
         <v>2470.4</v>
@@ -2025,28 +2025,28 @@
         <v>1333.8</v>
       </c>
       <c r="M9">
-        <v>33.0322615</v>
+        <v>37.75115599999999</v>
       </c>
       <c r="N9">
-        <v>1300.7677385</v>
+        <v>1296.048844</v>
       </c>
       <c r="O9">
-        <v>208.12283816</v>
+        <v>207.36781504</v>
       </c>
       <c r="P9">
-        <v>1092.64490034</v>
+        <v>1088.68102896</v>
       </c>
       <c r="Q9">
-        <v>1873.24490034</v>
+        <v>1869.28102896</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.118012589299518</v>
+        <v>0.1186793898022309</v>
       </c>
       <c r="T9">
-        <v>0.9940334728862986</v>
+        <v>1.003212232793174</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.37870673795678</v>
+        <v>35.33136839571218</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1125651986180524</v>
+        <v>0.1124210491875532</v>
       </c>
       <c r="C10">
-        <v>8718.192426731532</v>
+        <v>8634.535705291353</v>
       </c>
       <c r="D10">
-        <v>6998.312426731532</v>
+        <v>7008.470705291352</v>
       </c>
       <c r="E10">
-        <v>564.3199999999999</v>
+        <v>658.135</v>
       </c>
       <c r="F10">
-        <v>750.52</v>
+        <v>844.3349999999999</v>
       </c>
       <c r="G10">
         <v>2470.4</v>
@@ -2107,28 +2107,28 @@
         <v>1333.8</v>
       </c>
       <c r="M10">
-        <v>37.75115599999999</v>
+        <v>42.47005049999999</v>
       </c>
       <c r="N10">
-        <v>1296.048844</v>
+        <v>1291.3299495</v>
       </c>
       <c r="O10">
-        <v>207.36781504</v>
+        <v>206.61279192</v>
       </c>
       <c r="P10">
-        <v>1088.68102896</v>
+        <v>1084.71715758</v>
       </c>
       <c r="Q10">
-        <v>1869.28102896</v>
+        <v>1865.31715758</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1186793898022309</v>
+        <v>0.1193608452610474</v>
       </c>
       <c r="T10">
-        <v>1.003212232793174</v>
+        <v>1.012592723687014</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.33136839571218</v>
+        <v>31.40566079618861</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1124210491875532</v>
+        <v>0.1122768997570539</v>
       </c>
       <c r="C11">
-        <v>8634.535705291353</v>
+        <v>8550.908516864072</v>
       </c>
       <c r="D11">
-        <v>7008.470705291352</v>
+        <v>7018.658516864072</v>
       </c>
       <c r="E11">
-        <v>658.135</v>
+        <v>751.95</v>
       </c>
       <c r="F11">
-        <v>844.3349999999999</v>
+        <v>938.15</v>
       </c>
       <c r="G11">
         <v>2470.4</v>
@@ -2189,28 +2189,28 @@
         <v>1333.8</v>
       </c>
       <c r="M11">
-        <v>42.47005049999999</v>
+        <v>47.188945</v>
       </c>
       <c r="N11">
-        <v>1291.3299495</v>
+        <v>1286.611055</v>
       </c>
       <c r="O11">
-        <v>206.61279192</v>
+        <v>205.8577688</v>
       </c>
       <c r="P11">
-        <v>1084.71715758</v>
+        <v>1080.7532862</v>
       </c>
       <c r="Q11">
-        <v>1865.31715758</v>
+        <v>1861.3532862</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1193608452610474</v>
+        <v>0.1200574441745043</v>
       </c>
       <c r="T11">
-        <v>1.012592723687014</v>
+        <v>1.02218166993405</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.40566079618861</v>
+        <v>28.26509471656974</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1122768997570539</v>
+        <v>0.1121327503265546</v>
       </c>
       <c r="C12">
-        <v>8550.908516864072</v>
+        <v>8467.310990428517</v>
       </c>
       <c r="D12">
-        <v>7018.658516864072</v>
+        <v>7028.875990428518</v>
       </c>
       <c r="E12">
-        <v>751.95</v>
+        <v>845.7649999999999</v>
       </c>
       <c r="F12">
-        <v>938.1500000000001</v>
+        <v>1031.965</v>
       </c>
       <c r="G12">
         <v>2470.4</v>
@@ -2271,28 +2271,28 @@
         <v>1333.8</v>
       </c>
       <c r="M12">
-        <v>47.188945</v>
+        <v>51.90783949999999</v>
       </c>
       <c r="N12">
-        <v>1286.611055</v>
+        <v>1281.8921605</v>
       </c>
       <c r="O12">
-        <v>205.8577688</v>
+        <v>205.1027456800001</v>
       </c>
       <c r="P12">
-        <v>1080.7532862</v>
+        <v>1076.78941482</v>
       </c>
       <c r="Q12">
-        <v>1861.3532862</v>
+        <v>1857.38941482</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1200574441745043</v>
+        <v>0.1207696969961288</v>
       </c>
       <c r="T12">
-        <v>1.02218166993405</v>
+        <v>1.031986098119221</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.26509471656974</v>
+        <v>25.69554065142705</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1121327503265546</v>
+        <v>0.1119886008960553</v>
       </c>
       <c r="C13">
-        <v>8467.310990428517</v>
+        <v>8383.743255715655</v>
       </c>
       <c r="D13">
-        <v>7028.875990428518</v>
+        <v>7039.123255715656</v>
       </c>
       <c r="E13">
-        <v>845.7649999999999</v>
+        <v>939.5799999999999</v>
       </c>
       <c r="F13">
-        <v>1031.965</v>
+        <v>1125.78</v>
       </c>
       <c r="G13">
         <v>2470.4</v>
@@ -2353,28 +2353,28 @@
         <v>1333.8</v>
       </c>
       <c r="M13">
-        <v>51.90783949999999</v>
+        <v>56.626734</v>
       </c>
       <c r="N13">
-        <v>1281.8921605</v>
+        <v>1277.173266</v>
       </c>
       <c r="O13">
-        <v>205.1027456800001</v>
+        <v>204.3477225600001</v>
       </c>
       <c r="P13">
-        <v>1076.78941482</v>
+        <v>1072.82554344</v>
       </c>
       <c r="Q13">
-        <v>1857.38941482</v>
+        <v>1853.42554344</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1207696969961288</v>
+        <v>0.1214981373818811</v>
       </c>
       <c r="T13">
-        <v>1.031986098119221</v>
+        <v>1.042013354217693</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.69554065142705</v>
+        <v>23.55424559714145</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1119886008960553</v>
+        <v>0.1118444514655561</v>
       </c>
       <c r="C14">
-        <v>8383.743255715655</v>
+        <v>8300.205443214092</v>
       </c>
       <c r="D14">
-        <v>7039.123255715656</v>
+        <v>7049.400443214092</v>
       </c>
       <c r="E14">
-        <v>939.5799999999999</v>
+        <v>1033.395</v>
       </c>
       <c r="F14">
-        <v>1125.78</v>
+        <v>1219.595</v>
       </c>
       <c r="G14">
         <v>2470.4</v>
@@ -2435,28 +2435,28 @@
         <v>1333.8</v>
       </c>
       <c r="M14">
-        <v>56.626734</v>
+        <v>61.3456285</v>
       </c>
       <c r="N14">
-        <v>1277.173266</v>
+        <v>1272.4543715</v>
       </c>
       <c r="O14">
-        <v>204.3477225600001</v>
+        <v>203.59269944</v>
       </c>
       <c r="P14">
-        <v>1072.82554344</v>
+        <v>1068.86167206</v>
       </c>
       <c r="Q14">
-        <v>1853.42554344</v>
+        <v>1849.46167206</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1214981373818811</v>
+        <v>0.1222433235236277</v>
       </c>
       <c r="T14">
-        <v>1.042013354217693</v>
+        <v>1.052271121950611</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.55424559714145</v>
+        <v>21.7423805512075</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1118444514655561</v>
+        <v>0.1117003020350568</v>
       </c>
       <c r="C15">
-        <v>8300.205443214092</v>
+        <v>8216.697684175602</v>
       </c>
       <c r="D15">
-        <v>7049.400443214092</v>
+        <v>7059.707684175602</v>
       </c>
       <c r="E15">
-        <v>1033.395</v>
+        <v>1127.21</v>
       </c>
       <c r="F15">
-        <v>1219.595</v>
+        <v>1313.41</v>
       </c>
       <c r="G15">
         <v>2470.4</v>
@@ -2517,28 +2517,28 @@
         <v>1333.8</v>
       </c>
       <c r="M15">
-        <v>61.3456285</v>
+        <v>66.06452299999999</v>
       </c>
       <c r="N15">
-        <v>1272.4543715</v>
+        <v>1267.735477</v>
       </c>
       <c r="O15">
-        <v>203.59269944</v>
+        <v>202.83767632</v>
       </c>
       <c r="P15">
-        <v>1068.86167206</v>
+        <v>1064.89780068</v>
       </c>
       <c r="Q15">
-        <v>1849.46167206</v>
+        <v>1845.49780068</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1222433235236277</v>
+        <v>0.1230058395756474</v>
       </c>
       <c r="T15">
-        <v>1.052271121950611</v>
+        <v>1.062767442421505</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.7423805512075</v>
+        <v>20.18935336897839</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1117003020350568</v>
+        <v>0.1115561526045575</v>
       </c>
       <c r="C16">
-        <v>8216.697684175602</v>
+        <v>8133.220110620719</v>
       </c>
       <c r="D16">
-        <v>7059.707684175602</v>
+        <v>7070.045110620719</v>
       </c>
       <c r="E16">
-        <v>1127.21</v>
+        <v>1221.025</v>
       </c>
       <c r="F16">
-        <v>1313.41</v>
+        <v>1407.225</v>
       </c>
       <c r="G16">
         <v>2470.4</v>
@@ -2599,28 +2599,28 @@
         <v>1333.8</v>
       </c>
       <c r="M16">
-        <v>66.06452299999999</v>
+        <v>70.7834175</v>
       </c>
       <c r="N16">
-        <v>1267.735477</v>
+        <v>1263.0165825</v>
       </c>
       <c r="O16">
-        <v>202.83767632</v>
+        <v>202.0826532</v>
       </c>
       <c r="P16">
-        <v>1064.89780068</v>
+        <v>1060.9339293</v>
       </c>
       <c r="Q16">
-        <v>1845.49780068</v>
+        <v>1841.5339293</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1230058395756474</v>
+        <v>0.1237862971818324</v>
       </c>
       <c r="T16">
-        <v>1.062767442421505</v>
+        <v>1.073510735138772</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.18935336897839</v>
+        <v>18.84339647771316</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1115561526045575</v>
+        <v>0.1114120031740582</v>
       </c>
       <c r="C17">
-        <v>8133.220110620719</v>
+        <v>8049.77285534438</v>
       </c>
       <c r="D17">
-        <v>7070.045110620719</v>
+        <v>7080.41285534438</v>
       </c>
       <c r="E17">
-        <v>1221.025</v>
+        <v>1314.84</v>
       </c>
       <c r="F17">
-        <v>1407.225</v>
+        <v>1501.04</v>
       </c>
       <c r="G17">
         <v>2470.4</v>
@@ -2681,28 +2681,28 @@
         <v>1333.8</v>
       </c>
       <c r="M17">
-        <v>70.7834175</v>
+        <v>75.50231199999999</v>
       </c>
       <c r="N17">
-        <v>1263.0165825</v>
+        <v>1258.297688</v>
       </c>
       <c r="O17">
-        <v>202.0826532</v>
+        <v>201.32763008</v>
       </c>
       <c r="P17">
-        <v>1060.9339293</v>
+        <v>1056.97005792</v>
       </c>
       <c r="Q17">
-        <v>1841.5339293</v>
+        <v>1837.57005792</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1237862971818324</v>
+        <v>0.1245853371119741</v>
       </c>
       <c r="T17">
-        <v>1.073510735138772</v>
+        <v>1.084509820539785</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.84339647771316</v>
+        <v>17.66568419785609</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1114120031740582</v>
+        <v>0.1112678537435589</v>
       </c>
       <c r="C18">
-        <v>8049.77285534438</v>
+        <v>7966.356051921599</v>
       </c>
       <c r="D18">
-        <v>7080.41285534438</v>
+        <v>7090.811051921598</v>
       </c>
       <c r="E18">
-        <v>1314.84</v>
+        <v>1408.655</v>
       </c>
       <c r="F18">
-        <v>1501.04</v>
+        <v>1594.855</v>
       </c>
       <c r="G18">
         <v>2470.4</v>
@@ -2763,28 +2763,28 @@
         <v>1333.8</v>
       </c>
       <c r="M18">
-        <v>75.50231199999999</v>
+        <v>80.22120649999999</v>
       </c>
       <c r="N18">
-        <v>1258.297688</v>
+        <v>1253.5787935</v>
       </c>
       <c r="O18">
-        <v>201.32763008</v>
+        <v>200.5726069600001</v>
       </c>
       <c r="P18">
-        <v>1056.97005792</v>
+        <v>1053.00618654</v>
       </c>
       <c r="Q18">
-        <v>1837.57005792</v>
+        <v>1833.60618654</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1245853371119741</v>
+        <v>0.1254036310163361</v>
       </c>
       <c r="T18">
-        <v>1.084509820539785</v>
+        <v>1.095773944143231</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.66568419785609</v>
+        <v>16.62652630386456</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1112678537435589</v>
+        <v>0.1111237043130597</v>
       </c>
       <c r="C19">
-        <v>7966.356051921599</v>
+        <v>7882.969834713207</v>
       </c>
       <c r="D19">
-        <v>7090.811051921598</v>
+        <v>7101.239834713208</v>
       </c>
       <c r="E19">
-        <v>1408.655</v>
+        <v>1502.47</v>
       </c>
       <c r="F19">
-        <v>1594.855</v>
+        <v>1688.67</v>
       </c>
       <c r="G19">
         <v>2470.4</v>
@@ -2845,28 +2845,28 @@
         <v>1333.8</v>
       </c>
       <c r="M19">
-        <v>80.22120649999999</v>
+        <v>84.94010100000001</v>
       </c>
       <c r="N19">
-        <v>1253.5787935</v>
+        <v>1248.859899</v>
       </c>
       <c r="O19">
-        <v>200.5726069600001</v>
+        <v>199.8175838400001</v>
       </c>
       <c r="P19">
-        <v>1053.00618654</v>
+        <v>1049.04231516</v>
       </c>
       <c r="Q19">
-        <v>1833.60618654</v>
+        <v>1829.64231516</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1254036310163361</v>
+        <v>0.1262418833086094</v>
       </c>
       <c r="T19">
-        <v>1.095773944143231</v>
+        <v>1.107312802468712</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.62652630386456</v>
+        <v>15.7028303980943</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1111237043130597</v>
+        <v>0.1109795548825604</v>
       </c>
       <c r="C20">
-        <v>7882.969834713207</v>
+        <v>7799.614338871654</v>
       </c>
       <c r="D20">
-        <v>7101.239834713207</v>
+        <v>7111.699338871654</v>
       </c>
       <c r="E20">
-        <v>1502.47</v>
+        <v>1596.285</v>
       </c>
       <c r="F20">
-        <v>1688.67</v>
+        <v>1782.485</v>
       </c>
       <c r="G20">
         <v>2470.4</v>
@@ -2927,28 +2927,28 @@
         <v>1333.8</v>
       </c>
       <c r="M20">
-        <v>84.94010099999998</v>
+        <v>89.6589955</v>
       </c>
       <c r="N20">
-        <v>1248.859899</v>
+        <v>1244.1410045</v>
       </c>
       <c r="O20">
-        <v>199.8175838400001</v>
+        <v>199.0625607200001</v>
       </c>
       <c r="P20">
-        <v>1049.04231516</v>
+        <v>1045.07844378</v>
       </c>
       <c r="Q20">
-        <v>1829.64231516</v>
+        <v>1825.67844378</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1262418833086094</v>
+        <v>0.1271008331883462</v>
       </c>
       <c r="T20">
-        <v>1.107312802468712</v>
+        <v>1.119136570876304</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.7028303980943</v>
+        <v>14.87636564029986</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1109795548825604</v>
+        <v>0.1108354054520611</v>
       </c>
       <c r="C21">
-        <v>7799.614338871654</v>
+        <v>7716.289700346823</v>
       </c>
       <c r="D21">
-        <v>7111.699338871654</v>
+        <v>7122.189700346823</v>
       </c>
       <c r="E21">
-        <v>1596.285</v>
+        <v>1690.1</v>
       </c>
       <c r="F21">
-        <v>1782.485</v>
+        <v>1876.3</v>
       </c>
       <c r="G21">
         <v>2470.4</v>
@@ -3009,28 +3009,28 @@
         <v>1333.8</v>
       </c>
       <c r="M21">
-        <v>89.6589955</v>
+        <v>94.37789000000001</v>
       </c>
       <c r="N21">
-        <v>1244.1410045</v>
+        <v>1239.42211</v>
       </c>
       <c r="O21">
-        <v>199.0625607200001</v>
+        <v>198.3075376</v>
       </c>
       <c r="P21">
-        <v>1045.07844378</v>
+        <v>1041.1145724</v>
       </c>
       <c r="Q21">
-        <v>1825.67844378</v>
+        <v>1821.7145724</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1271008331883462</v>
+        <v>0.1279812568150764</v>
       </c>
       <c r="T21">
-        <v>1.119136570876304</v>
+        <v>1.131255933494085</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.87636564029986</v>
+        <v>14.13254735828487</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1108354054520611</v>
+        <v>0.1106912560215619</v>
       </c>
       <c r="C22">
-        <v>7716.289700346823</v>
+        <v>7632.996055891941</v>
       </c>
       <c r="D22">
-        <v>7122.189700346823</v>
+        <v>7132.71105589194</v>
       </c>
       <c r="E22">
-        <v>1690.1</v>
+        <v>1783.915</v>
       </c>
       <c r="F22">
-        <v>1876.3</v>
+        <v>1970.115</v>
       </c>
       <c r="G22">
         <v>2470.4</v>
@@ -3091,28 +3091,28 @@
         <v>1333.8</v>
       </c>
       <c r="M22">
-        <v>94.37789000000001</v>
+        <v>99.09678450000001</v>
       </c>
       <c r="N22">
-        <v>1239.42211</v>
+        <v>1234.7032155</v>
       </c>
       <c r="O22">
-        <v>198.3075376</v>
+        <v>197.55251448</v>
       </c>
       <c r="P22">
-        <v>1041.1145724</v>
+        <v>1037.15070102</v>
       </c>
       <c r="Q22">
-        <v>1821.7145724</v>
+        <v>1817.75070102</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1279812568150764</v>
+        <v>0.1288839696475467</v>
       </c>
       <c r="T22">
-        <v>1.131255933494085</v>
+        <v>1.143682115418647</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.13254735828487</v>
+        <v>13.45956891265226</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1106912560215619</v>
+        <v>0.1105471065910626</v>
       </c>
       <c r="C23">
-        <v>7632.996055891941</v>
+        <v>7549.733543069509</v>
       </c>
       <c r="D23">
-        <v>7132.71105589194</v>
+        <v>7143.26354306951</v>
       </c>
       <c r="E23">
-        <v>1783.915</v>
+        <v>1877.73</v>
       </c>
       <c r="F23">
-        <v>1970.115</v>
+        <v>2063.93</v>
       </c>
       <c r="G23">
         <v>2470.4</v>
@@ -3173,28 +3173,28 @@
         <v>1333.8</v>
       </c>
       <c r="M23">
-        <v>99.0967845</v>
+        <v>103.815679</v>
       </c>
       <c r="N23">
-        <v>1234.7032155</v>
+        <v>1229.984321</v>
       </c>
       <c r="O23">
-        <v>197.55251448</v>
+        <v>196.79749136</v>
       </c>
       <c r="P23">
-        <v>1037.15070102</v>
+        <v>1033.18682964</v>
       </c>
       <c r="Q23">
-        <v>1817.75070102</v>
+        <v>1813.78682964</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1288839696475467</v>
+        <v>0.1298098289629007</v>
       </c>
       <c r="T23">
-        <v>1.143682115418647</v>
+        <v>1.156426917392555</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.45956891265226</v>
+        <v>12.84777032571352</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1105471065910626</v>
+        <v>0.1104029571605633</v>
       </c>
       <c r="C24">
-        <v>7549.733543069509</v>
+        <v>7466.502300257304</v>
       </c>
       <c r="D24">
-        <v>7143.26354306951</v>
+        <v>7153.847300257304</v>
       </c>
       <c r="E24">
-        <v>1877.73</v>
+        <v>1971.545</v>
       </c>
       <c r="F24">
-        <v>2063.93</v>
+        <v>2157.745</v>
       </c>
       <c r="G24">
         <v>2470.4</v>
@@ -3255,28 +3255,28 @@
         <v>1333.8</v>
       </c>
       <c r="M24">
-        <v>103.815679</v>
+        <v>108.5345735</v>
       </c>
       <c r="N24">
-        <v>1229.984321</v>
+        <v>1225.2654265</v>
       </c>
       <c r="O24">
-        <v>196.79749136</v>
+        <v>196.04246824</v>
       </c>
       <c r="P24">
-        <v>1033.18682964</v>
+        <v>1029.22295826</v>
       </c>
       <c r="Q24">
-        <v>1813.78682964</v>
+        <v>1809.82295826</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1298098289629007</v>
+        <v>0.1307597365721601</v>
       </c>
       <c r="T24">
-        <v>1.156426917392555</v>
+        <v>1.169502753183968</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.84777032571352</v>
+        <v>12.28917161589989</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1104029571605633</v>
+        <v>0.1102588077300641</v>
       </c>
       <c r="C25">
-        <v>7466.502300257304</v>
+        <v>7383.302466654414</v>
       </c>
       <c r="D25">
-        <v>7153.847300257304</v>
+        <v>7164.462466654415</v>
       </c>
       <c r="E25">
-        <v>1971.545</v>
+        <v>2065.360000000001</v>
       </c>
       <c r="F25">
-        <v>2157.745</v>
+        <v>2251.56</v>
       </c>
       <c r="G25">
         <v>2470.4</v>
@@ -3337,28 +3337,28 @@
         <v>1333.8</v>
       </c>
       <c r="M25">
-        <v>108.5345735</v>
+        <v>113.253468</v>
       </c>
       <c r="N25">
-        <v>1225.2654265</v>
+        <v>1220.546532</v>
       </c>
       <c r="O25">
-        <v>196.04246824</v>
+        <v>195.28744512</v>
       </c>
       <c r="P25">
-        <v>1029.22295826</v>
+        <v>1025.25908688</v>
       </c>
       <c r="Q25">
-        <v>1809.82295826</v>
+        <v>1805.85908688</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1307597365721601</v>
+        <v>0.1317346417500843</v>
       </c>
       <c r="T25">
-        <v>1.169502753183968</v>
+        <v>1.18292268991726</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.28917161589989</v>
+        <v>11.77712279857072</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.110258807730064</v>
+        <v>0.1101146582995648</v>
       </c>
       <c r="C26">
-        <v>7383.302466654417</v>
+        <v>7300.134182287375</v>
       </c>
       <c r="D26">
-        <v>7164.462466654417</v>
+        <v>7175.109182287375</v>
       </c>
       <c r="E26">
-        <v>2065.36</v>
+        <v>2159.175</v>
       </c>
       <c r="F26">
-        <v>2251.56</v>
+        <v>2345.375</v>
       </c>
       <c r="G26">
         <v>2470.4</v>
@@ -3419,28 +3419,28 @@
         <v>1333.8</v>
       </c>
       <c r="M26">
-        <v>113.253468</v>
+        <v>117.9723625</v>
       </c>
       <c r="N26">
-        <v>1220.546532</v>
+        <v>1215.8276375</v>
       </c>
       <c r="O26">
-        <v>195.2874451200001</v>
+        <v>194.5324220000001</v>
       </c>
       <c r="P26">
-        <v>1025.25908688</v>
+        <v>1021.2952155</v>
       </c>
       <c r="Q26">
-        <v>1805.85908688</v>
+        <v>1801.8952155</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1317346417500843</v>
+        <v>0.1327355443994197</v>
       </c>
       <c r="T26">
-        <v>1.18292268991726</v>
+        <v>1.196700491630107</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.77712279857073</v>
+        <v>11.3060378866279</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1101146582995648</v>
+        <v>0.1099705088690655</v>
       </c>
       <c r="C27">
-        <v>7300.134182287375</v>
+        <v>7216.997588016278</v>
       </c>
       <c r="D27">
-        <v>7175.109182287375</v>
+        <v>7185.787588016279</v>
       </c>
       <c r="E27">
-        <v>2159.175</v>
+        <v>2252.99</v>
       </c>
       <c r="F27">
-        <v>2345.375</v>
+        <v>2439.19</v>
       </c>
       <c r="G27">
         <v>2470.4</v>
@@ -3501,28 +3501,28 @@
         <v>1333.8</v>
       </c>
       <c r="M27">
-        <v>117.9723625</v>
+        <v>122.691257</v>
       </c>
       <c r="N27">
-        <v>1215.8276375</v>
+        <v>1211.108743</v>
       </c>
       <c r="O27">
-        <v>194.5324220000001</v>
+        <v>193.77739888</v>
       </c>
       <c r="P27">
-        <v>1021.2952155</v>
+        <v>1017.33134412</v>
       </c>
       <c r="Q27">
-        <v>1801.8952155</v>
+        <v>1797.93134412</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1327355443994197</v>
+        <v>0.1337634984717101</v>
       </c>
       <c r="T27">
-        <v>1.196700491630107</v>
+        <v>1.21085066636222</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.3060378866279</v>
+        <v>10.87119027560375</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1099705088690655</v>
+        <v>0.1098263594385662</v>
       </c>
       <c r="C28">
-        <v>7216.997588016278</v>
+        <v>7133.892825541029</v>
       </c>
       <c r="D28">
-        <v>7185.787588016279</v>
+        <v>7196.49782554103</v>
       </c>
       <c r="E28">
-        <v>2252.99</v>
+        <v>2346.805</v>
       </c>
       <c r="F28">
-        <v>2439.19</v>
+        <v>2533.005</v>
       </c>
       <c r="G28">
         <v>2470.4</v>
@@ -3583,28 +3583,28 @@
         <v>1333.8</v>
       </c>
       <c r="M28">
-        <v>122.691257</v>
+        <v>127.4101515</v>
       </c>
       <c r="N28">
-        <v>1211.108743</v>
+        <v>1206.3898485</v>
       </c>
       <c r="O28">
-        <v>193.77739888</v>
+        <v>193.02237576</v>
       </c>
       <c r="P28">
-        <v>1017.33134412</v>
+        <v>1013.36747274</v>
       </c>
       <c r="Q28">
-        <v>1797.93134412</v>
+        <v>1793.96747274</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1337634984717101</v>
+        <v>0.1348196156692688</v>
       </c>
       <c r="T28">
-        <v>1.21085066636222</v>
+        <v>1.225388517114391</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.87119027560375</v>
+        <v>10.46855359872954</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1098263594385662</v>
+        <v>0.109682210008067</v>
       </c>
       <c r="C29">
-        <v>7133.892825541029</v>
+        <v>7050.820037407582</v>
       </c>
       <c r="D29">
-        <v>7196.49782554103</v>
+        <v>7207.240037407581</v>
       </c>
       <c r="E29">
-        <v>2346.805</v>
+        <v>2440.62</v>
       </c>
       <c r="F29">
-        <v>2533.005</v>
+        <v>2626.82</v>
       </c>
       <c r="G29">
         <v>2470.4</v>
@@ -3665,28 +3665,28 @@
         <v>1333.8</v>
       </c>
       <c r="M29">
-        <v>127.4101515</v>
+        <v>132.129046</v>
       </c>
       <c r="N29">
-        <v>1206.3898485</v>
+        <v>1201.670954</v>
       </c>
       <c r="O29">
-        <v>193.02237576</v>
+        <v>192.26735264</v>
       </c>
       <c r="P29">
-        <v>1013.36747274</v>
+        <v>1009.40360136</v>
       </c>
       <c r="Q29">
-        <v>1793.96747274</v>
+        <v>1790.00360136</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1348196156692688</v>
+        <v>0.1359050694556485</v>
       </c>
       <c r="T29">
-        <v>1.225388517114391</v>
+        <v>1.240330197054121</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.46855359872954</v>
+        <v>10.09467668448919</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.109682210008067</v>
+        <v>0.1095380605775677</v>
       </c>
       <c r="C30">
-        <v>7050.820037407582</v>
+        <v>6967.779367014286</v>
       </c>
       <c r="D30">
-        <v>7207.240037407581</v>
+        <v>7218.014367014286</v>
       </c>
       <c r="E30">
-        <v>2440.62</v>
+        <v>2534.435</v>
       </c>
       <c r="F30">
-        <v>2626.82</v>
+        <v>2720.635</v>
       </c>
       <c r="G30">
         <v>2470.4</v>
@@ -3747,28 +3747,28 @@
         <v>1333.8</v>
       </c>
       <c r="M30">
-        <v>132.129046</v>
+        <v>136.8479405</v>
       </c>
       <c r="N30">
-        <v>1201.670954</v>
+        <v>1196.9520595</v>
       </c>
       <c r="O30">
-        <v>192.26735264</v>
+        <v>191.51232952</v>
       </c>
       <c r="P30">
-        <v>1009.40360136</v>
+        <v>1005.43972998</v>
       </c>
       <c r="Q30">
-        <v>1790.00360136</v>
+        <v>1786.03972998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1359050694556485</v>
+        <v>0.1370210994050249</v>
       </c>
       <c r="T30">
-        <v>1.240330197054121</v>
+        <v>1.255692769386521</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.09467668448919</v>
+        <v>9.746584385024049</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1095380605775677</v>
+        <v>0.1093939111470684</v>
       </c>
       <c r="C31">
-        <v>6967.779367014286</v>
+        <v>6884.770958618249</v>
       </c>
       <c r="D31">
-        <v>7218.014367014286</v>
+        <v>7228.820958618248</v>
       </c>
       <c r="E31">
-        <v>2534.435</v>
+        <v>2628.25</v>
       </c>
       <c r="F31">
-        <v>2720.635</v>
+        <v>2814.45</v>
       </c>
       <c r="G31">
         <v>2470.4</v>
@@ -3829,28 +3829,28 @@
         <v>1333.8</v>
       </c>
       <c r="M31">
-        <v>136.8479405</v>
+        <v>141.566835</v>
       </c>
       <c r="N31">
-        <v>1196.9520595</v>
+        <v>1192.233165</v>
       </c>
       <c r="O31">
-        <v>191.51232952</v>
+        <v>190.7573064</v>
       </c>
       <c r="P31">
-        <v>1005.43972998</v>
+        <v>1001.4758586</v>
       </c>
       <c r="Q31">
-        <v>1786.03972998</v>
+        <v>1782.0758586</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1370210994050249</v>
+        <v>0.1381690159243834</v>
       </c>
       <c r="T31">
-        <v>1.255692769386521</v>
+        <v>1.271494272356989</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.746584385024049</v>
+        <v>9.42169823885658</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1093939111470684</v>
+        <v>0.1092497617165691</v>
       </c>
       <c r="C32">
-        <v>6884.770958618249</v>
+        <v>6801.794957341788</v>
       </c>
       <c r="D32">
-        <v>7228.820958618248</v>
+        <v>7239.659957341788</v>
       </c>
       <c r="E32">
-        <v>2628.25</v>
+        <v>2722.065</v>
       </c>
       <c r="F32">
-        <v>2814.45</v>
+        <v>2908.265</v>
       </c>
       <c r="G32">
         <v>2470.4</v>
@@ -3911,28 +3911,28 @@
         <v>1333.8</v>
       </c>
       <c r="M32">
-        <v>141.566835</v>
+        <v>146.2857295</v>
       </c>
       <c r="N32">
-        <v>1192.233165</v>
+        <v>1187.5142705</v>
       </c>
       <c r="O32">
-        <v>190.7573064</v>
+        <v>190.0022832800001</v>
       </c>
       <c r="P32">
-        <v>1001.4758586</v>
+        <v>997.5119872200003</v>
       </c>
       <c r="Q32">
-        <v>1782.0758586</v>
+        <v>1778.11198722</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1381690159243834</v>
+        <v>0.139350205386332</v>
       </c>
       <c r="T32">
-        <v>1.271494272356989</v>
+        <v>1.287753789906311</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.42169823885658</v>
+        <v>9.117772489216048</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1092497617165691</v>
+        <v>0.1091056122860698</v>
       </c>
       <c r="C33">
-        <v>6801.794957341788</v>
+        <v>6718.851509178921</v>
       </c>
       <c r="D33">
-        <v>7239.659957341788</v>
+        <v>7250.531509178921</v>
       </c>
       <c r="E33">
-        <v>2722.065</v>
+        <v>2815.88</v>
       </c>
       <c r="F33">
-        <v>2908.265</v>
+        <v>3002.08</v>
       </c>
       <c r="G33">
         <v>2470.4</v>
@@ -3993,28 +3993,28 @@
         <v>1333.8</v>
       </c>
       <c r="M33">
-        <v>146.2857295</v>
+        <v>151.004624</v>
       </c>
       <c r="N33">
-        <v>1187.5142705</v>
+        <v>1182.795376</v>
       </c>
       <c r="O33">
-        <v>190.0022832800001</v>
+        <v>189.2472601600001</v>
       </c>
       <c r="P33">
-        <v>997.5119872200003</v>
+        <v>993.5481158400003</v>
       </c>
       <c r="Q33">
-        <v>1778.11198722</v>
+        <v>1774.14811584</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.139350205386332</v>
+        <v>0.1405661357148086</v>
       </c>
       <c r="T33">
-        <v>1.287753789906311</v>
+        <v>1.304491528560025</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.117772489216048</v>
+        <v>8.832842098928047</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1091056122860698</v>
+        <v>0.1093772628555705</v>
       </c>
       <c r="C34">
-        <v>6718.851509178921</v>
+        <v>6604.576132172004</v>
       </c>
       <c r="D34">
-        <v>7250.531509178921</v>
+        <v>7230.071132172005</v>
       </c>
       <c r="E34">
-        <v>2815.88</v>
+        <v>2909.695</v>
       </c>
       <c r="F34">
-        <v>3002.08</v>
+        <v>3095.895</v>
       </c>
       <c r="G34">
         <v>2470.4</v>
@@ -4075,45 +4075,45 @@
         <v>1333.8</v>
       </c>
       <c r="M34">
-        <v>151.004624</v>
+        <v>160.367361</v>
       </c>
       <c r="N34">
-        <v>1182.795376</v>
+        <v>1173.432639</v>
       </c>
       <c r="O34">
-        <v>189.2472601600001</v>
+        <v>187.74922224</v>
       </c>
       <c r="P34">
-        <v>993.5481158400003</v>
+        <v>985.6834167600001</v>
       </c>
       <c r="Q34">
-        <v>1774.14811584</v>
+        <v>1766.28341676</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1405661357148086</v>
+        <v>0.1418183624710008</v>
       </c>
       <c r="T34">
-        <v>1.304491528560025</v>
+        <v>1.321728901203402</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.16</v>
       </c>
       <c r="W34">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>8.832842098928047</v>
+        <v>8.317153762977993</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1093772628555705</v>
+        <v>0.1092457134250713</v>
       </c>
       <c r="C35">
-        <v>6604.576132172004</v>
+        <v>6520.654828961903</v>
       </c>
       <c r="D35">
-        <v>7230.071132172005</v>
+        <v>7239.964828961904</v>
       </c>
       <c r="E35">
-        <v>2909.695</v>
+        <v>3003.51</v>
       </c>
       <c r="F35">
-        <v>3095.895</v>
+        <v>3189.71</v>
       </c>
       <c r="G35">
         <v>2470.4</v>
@@ -4157,28 +4157,28 @@
         <v>1333.8</v>
       </c>
       <c r="M35">
-        <v>160.367361</v>
+        <v>165.226978</v>
       </c>
       <c r="N35">
-        <v>1173.432639</v>
+        <v>1168.573022</v>
       </c>
       <c r="O35">
-        <v>187.74922224</v>
+        <v>186.9716835200001</v>
       </c>
       <c r="P35">
-        <v>985.6834167600001</v>
+        <v>981.6013384800002</v>
       </c>
       <c r="Q35">
-        <v>1766.28341676</v>
+        <v>1762.20133848</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1418183624710008</v>
+        <v>0.1431085354925323</v>
       </c>
       <c r="T35">
-        <v>1.321728901203402</v>
+        <v>1.339488618472336</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.317153762977993</v>
+        <v>8.07253159347864</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1092457134250713</v>
+        <v>0.109114163994572</v>
       </c>
       <c r="C36">
-        <v>6520.654828961903</v>
+        <v>6436.760640109325</v>
       </c>
       <c r="D36">
-        <v>7239.964828961904</v>
+        <v>7249.885640109324</v>
       </c>
       <c r="E36">
-        <v>3003.51</v>
+        <v>3097.325</v>
       </c>
       <c r="F36">
-        <v>3189.71</v>
+        <v>3283.525</v>
       </c>
       <c r="G36">
         <v>2470.4</v>
@@ -4239,28 +4239,28 @@
         <v>1333.8</v>
       </c>
       <c r="M36">
-        <v>165.226978</v>
+        <v>170.086595</v>
       </c>
       <c r="N36">
-        <v>1168.573022</v>
+        <v>1163.713405</v>
       </c>
       <c r="O36">
-        <v>186.9716835200001</v>
+        <v>186.1941448</v>
       </c>
       <c r="P36">
-        <v>981.6013384800002</v>
+        <v>977.5192602000002</v>
       </c>
       <c r="Q36">
-        <v>1762.20133848</v>
+        <v>1758.1192602</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1431085354925323</v>
+        <v>0.1444384061454954</v>
       </c>
       <c r="T36">
-        <v>1.339488618472336</v>
+        <v>1.357794788580314</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.07253159347864</v>
+        <v>7.841887833664965</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.109114163994572</v>
+        <v>0.1089826145640727</v>
       </c>
       <c r="C37">
-        <v>6436.760640109325</v>
+        <v>6352.893677230357</v>
       </c>
       <c r="D37">
-        <v>7249.885640109324</v>
+        <v>7259.833677230357</v>
       </c>
       <c r="E37">
-        <v>3097.325</v>
+        <v>3191.140000000001</v>
       </c>
       <c r="F37">
-        <v>3283.525</v>
+        <v>3377.340000000001</v>
       </c>
       <c r="G37">
         <v>2470.4</v>
@@ -4321,28 +4321,28 @@
         <v>1333.8</v>
       </c>
       <c r="M37">
-        <v>170.086595</v>
+        <v>174.946212</v>
       </c>
       <c r="N37">
-        <v>1163.713405</v>
+        <v>1158.853788</v>
       </c>
       <c r="O37">
-        <v>186.1941448</v>
+        <v>185.41660608</v>
       </c>
       <c r="P37">
-        <v>977.5192602000002</v>
+        <v>973.4371819200001</v>
       </c>
       <c r="Q37">
-        <v>1758.1192602</v>
+        <v>1754.03718192</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1444384061454954</v>
+        <v>0.1458098352563637</v>
       </c>
       <c r="T37">
-        <v>1.357794788580314</v>
+        <v>1.376673026504166</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.841887833664965</v>
+        <v>7.624057616063158</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1089826145640727</v>
+        <v>0.1088510651335735</v>
       </c>
       <c r="C38">
-        <v>6352.893677230357</v>
+        <v>6269.054052554561</v>
       </c>
       <c r="D38">
-        <v>7259.833677230357</v>
+        <v>7269.80905255456</v>
       </c>
       <c r="E38">
-        <v>3191.14</v>
+        <v>3284.955</v>
       </c>
       <c r="F38">
-        <v>3377.34</v>
+        <v>3471.155</v>
       </c>
       <c r="G38">
         <v>2470.4</v>
@@ -4403,28 +4403,28 @@
         <v>1333.8</v>
       </c>
       <c r="M38">
-        <v>174.946212</v>
+        <v>179.805829</v>
       </c>
       <c r="N38">
-        <v>1158.853788</v>
+        <v>1153.994171</v>
       </c>
       <c r="O38">
-        <v>185.41660608</v>
+        <v>184.63906736</v>
       </c>
       <c r="P38">
-        <v>973.4371819200001</v>
+        <v>969.3551036400003</v>
       </c>
       <c r="Q38">
-        <v>1754.03718192</v>
+        <v>1749.95510364</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1458098352563637</v>
+        <v>0.147224801799323</v>
       </c>
       <c r="T38">
-        <v>1.376673026504166</v>
+        <v>1.396150573568458</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.62405761606316</v>
+        <v>7.41800200481821</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1088510651335735</v>
+        <v>0.1087195157030742</v>
       </c>
       <c r="C39">
-        <v>6269.054052554561</v>
+        <v>6185.241878929172</v>
       </c>
       <c r="D39">
-        <v>7269.80905255456</v>
+        <v>7279.811878929172</v>
       </c>
       <c r="E39">
-        <v>3284.955</v>
+        <v>3378.77</v>
       </c>
       <c r="F39">
-        <v>3471.155</v>
+        <v>3564.97</v>
       </c>
       <c r="G39">
         <v>2470.4</v>
@@ -4485,28 +4485,28 @@
         <v>1333.8</v>
       </c>
       <c r="M39">
-        <v>179.805829</v>
+        <v>184.665446</v>
       </c>
       <c r="N39">
-        <v>1153.994171</v>
+        <v>1149.134554</v>
       </c>
       <c r="O39">
-        <v>184.63906736</v>
+        <v>183.86152864</v>
       </c>
       <c r="P39">
-        <v>969.3551036400003</v>
+        <v>965.2730253600001</v>
       </c>
       <c r="Q39">
-        <v>1749.95510364</v>
+        <v>1745.87302536</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.147224801799323</v>
+        <v>0.1486854124243132</v>
       </c>
       <c r="T39">
-        <v>1.396150573568458</v>
+        <v>1.416256428602566</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.41800200481821</v>
+        <v>7.222791425744046</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1087195157030742</v>
+        <v>0.1085879662725749</v>
       </c>
       <c r="C40">
-        <v>6185.241878929172</v>
+        <v>6101.457269823379</v>
       </c>
       <c r="D40">
-        <v>7279.811878929172</v>
+        <v>7289.842269823378</v>
       </c>
       <c r="E40">
-        <v>3378.77</v>
+        <v>3472.585</v>
       </c>
       <c r="F40">
-        <v>3564.97</v>
+        <v>3658.785</v>
       </c>
       <c r="G40">
         <v>2470.4</v>
@@ -4567,28 +4567,28 @@
         <v>1333.8</v>
       </c>
       <c r="M40">
-        <v>184.665446</v>
+        <v>189.525063</v>
       </c>
       <c r="N40">
-        <v>1149.134554</v>
+        <v>1144.274937</v>
       </c>
       <c r="O40">
-        <v>183.86152864</v>
+        <v>183.08398992</v>
       </c>
       <c r="P40">
-        <v>965.2730253600001</v>
+        <v>961.1909470800001</v>
       </c>
       <c r="Q40">
-        <v>1745.87302536</v>
+        <v>1741.79094708</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1486854124243132</v>
+        <v>0.150193911922254</v>
       </c>
       <c r="T40">
-        <v>1.416256428602566</v>
+        <v>1.437021491998448</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.222791425744046</v>
+        <v>7.037591645596763</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1085879662725749</v>
+        <v>0.1084564168420756</v>
       </c>
       <c r="C41">
-        <v>6101.457269823379</v>
+        <v>6017.70033933259</v>
       </c>
       <c r="D41">
-        <v>7289.842269823378</v>
+        <v>7299.90033933259</v>
       </c>
       <c r="E41">
-        <v>3472.585</v>
+        <v>3566.400000000001</v>
       </c>
       <c r="F41">
-        <v>3658.785</v>
+        <v>3752.6</v>
       </c>
       <c r="G41">
         <v>2470.4</v>
@@ -4649,28 +4649,28 @@
         <v>1333.8</v>
       </c>
       <c r="M41">
-        <v>189.525063</v>
+        <v>194.38468</v>
       </c>
       <c r="N41">
-        <v>1144.274937</v>
+        <v>1139.41532</v>
       </c>
       <c r="O41">
-        <v>183.08398992</v>
+        <v>182.3064512</v>
       </c>
       <c r="P41">
-        <v>961.1909470800001</v>
+        <v>957.1088688</v>
       </c>
       <c r="Q41">
-        <v>1741.79094708</v>
+        <v>1737.7088688</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.150193911922254</v>
+        <v>0.1517526947367927</v>
       </c>
       <c r="T41">
-        <v>1.437021491998448</v>
+        <v>1.458478724174193</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.037591645596763</v>
+        <v>6.861651854456843</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1084564168420756</v>
+        <v>0.1089103474115764</v>
       </c>
       <c r="C42">
-        <v>6017.70033933259</v>
+        <v>5889.295294340807</v>
       </c>
       <c r="D42">
-        <v>7299.90033933259</v>
+        <v>7265.310294340808</v>
       </c>
       <c r="E42">
-        <v>3566.400000000001</v>
+        <v>3660.215000000001</v>
       </c>
       <c r="F42">
-        <v>3752.6</v>
+        <v>3846.415</v>
       </c>
       <c r="G42">
         <v>2470.4</v>
@@ -4731,45 +4731,45 @@
         <v>1333.8</v>
       </c>
       <c r="M42">
-        <v>194.38468</v>
+        <v>205.7832025</v>
       </c>
       <c r="N42">
-        <v>1139.41532</v>
+        <v>1128.0167975</v>
       </c>
       <c r="O42">
-        <v>182.3064512</v>
+        <v>180.4826876</v>
       </c>
       <c r="P42">
-        <v>957.1088688</v>
+        <v>947.5341099000002</v>
       </c>
       <c r="Q42">
-        <v>1737.7088688</v>
+        <v>1728.1341099</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1517526947367927</v>
+        <v>0.1533643176467396</v>
       </c>
       <c r="T42">
-        <v>1.458478724174193</v>
+        <v>1.480663320152505</v>
       </c>
       <c r="U42">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V42">
         <v>0.16</v>
       </c>
       <c r="W42">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.861651854456843</v>
+        <v>6.481578592402362</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1089103474115764</v>
+        <v>0.1087930779810771</v>
       </c>
       <c r="C43">
-        <v>5889.295294340807</v>
+        <v>5804.384920872898</v>
       </c>
       <c r="D43">
-        <v>7265.310294340808</v>
+        <v>7274.214920872898</v>
       </c>
       <c r="E43">
-        <v>3660.215000000001</v>
+        <v>3754.030000000001</v>
       </c>
       <c r="F43">
-        <v>3846.415</v>
+        <v>3940.23</v>
       </c>
       <c r="G43">
         <v>2470.4</v>
@@ -4813,28 +4813,28 @@
         <v>1333.8</v>
       </c>
       <c r="M43">
-        <v>205.7832025</v>
+        <v>210.802305</v>
       </c>
       <c r="N43">
-        <v>1128.0167975</v>
+        <v>1122.997695</v>
       </c>
       <c r="O43">
-        <v>180.4826876</v>
+        <v>179.6796312</v>
       </c>
       <c r="P43">
-        <v>947.5341099000002</v>
+        <v>943.3180638000002</v>
       </c>
       <c r="Q43">
-        <v>1728.1341099</v>
+        <v>1723.9180638</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1533643176467396</v>
+        <v>0.1550315137604777</v>
       </c>
       <c r="T43">
-        <v>1.480663320152505</v>
+        <v>1.503612902199035</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.481578592402362</v>
+        <v>6.327255292583258</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1087930779810771</v>
+        <v>0.1086758085505778</v>
       </c>
       <c r="C44">
-        <v>5804.384920872897</v>
+        <v>5719.496401853952</v>
       </c>
       <c r="D44">
-        <v>7274.214920872896</v>
+        <v>7283.141401853953</v>
       </c>
       <c r="E44">
-        <v>3754.03</v>
+        <v>3847.845</v>
       </c>
       <c r="F44">
-        <v>3940.23</v>
+        <v>4034.045</v>
       </c>
       <c r="G44">
         <v>2470.4</v>
@@ -4895,28 +4895,28 @@
         <v>1333.8</v>
       </c>
       <c r="M44">
-        <v>210.802305</v>
+        <v>215.8214075</v>
       </c>
       <c r="N44">
-        <v>1122.997695</v>
+        <v>1117.9785925</v>
       </c>
       <c r="O44">
-        <v>179.6796312</v>
+        <v>178.8765748</v>
       </c>
       <c r="P44">
-        <v>943.3180638000002</v>
+        <v>939.1020177</v>
       </c>
       <c r="Q44">
-        <v>1723.9180638</v>
+        <v>1719.7020177</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1550315137604777</v>
+        <v>0.1567572079834698</v>
       </c>
       <c r="T44">
-        <v>1.503612902199035</v>
+        <v>1.527367732738426</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.327255292583258</v>
+        <v>6.180109820662717</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1086758085505778</v>
+        <v>0.1085585391200785</v>
       </c>
       <c r="C45">
-        <v>5719.496401853952</v>
+        <v>5634.629817838241</v>
       </c>
       <c r="D45">
-        <v>7283.141401853953</v>
+        <v>7292.08981783824</v>
       </c>
       <c r="E45">
-        <v>3847.845</v>
+        <v>3941.66</v>
       </c>
       <c r="F45">
-        <v>4034.045</v>
+        <v>4127.86</v>
       </c>
       <c r="G45">
         <v>2470.4</v>
@@ -4977,28 +4977,28 @@
         <v>1333.8</v>
       </c>
       <c r="M45">
-        <v>215.8214075</v>
+        <v>220.84051</v>
       </c>
       <c r="N45">
-        <v>1117.9785925</v>
+        <v>1112.95949</v>
       </c>
       <c r="O45">
-        <v>178.8765748</v>
+        <v>178.0735184</v>
       </c>
       <c r="P45">
-        <v>939.1020177</v>
+        <v>934.8859716000002</v>
       </c>
       <c r="Q45">
-        <v>1719.7020177</v>
+        <v>1715.4859716</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1567572079834698</v>
+        <v>0.1585445341429974</v>
       </c>
       <c r="T45">
-        <v>1.527367732738426</v>
+        <v>1.551970950082795</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.180109820662717</v>
+        <v>6.03965277928402</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1085585391200785</v>
+        <v>0.1084412696895793</v>
       </c>
       <c r="C46">
-        <v>5634.629817838241</v>
+        <v>5549.785249776404</v>
       </c>
       <c r="D46">
-        <v>7292.08981783824</v>
+        <v>7301.060249776404</v>
       </c>
       <c r="E46">
-        <v>3941.66</v>
+        <v>4035.475</v>
       </c>
       <c r="F46">
-        <v>4127.86</v>
+        <v>4221.675</v>
       </c>
       <c r="G46">
         <v>2470.4</v>
@@ -5059,28 +5059,28 @@
         <v>1333.8</v>
       </c>
       <c r="M46">
-        <v>220.84051</v>
+        <v>225.8596125</v>
       </c>
       <c r="N46">
-        <v>1112.95949</v>
+        <v>1107.9403875</v>
       </c>
       <c r="O46">
-        <v>178.0735184</v>
+        <v>177.270462</v>
       </c>
       <c r="P46">
-        <v>934.8859716000002</v>
+        <v>930.6699255000002</v>
       </c>
       <c r="Q46">
-        <v>1715.4859716</v>
+        <v>1711.2699255</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1585445341429974</v>
+        <v>0.1603968539810532</v>
       </c>
       <c r="T46">
-        <v>1.551970950082795</v>
+        <v>1.57746882987605</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.03965277928402</v>
+        <v>5.905438273077708</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1084412696895793</v>
+        <v>0.10832400025908</v>
       </c>
       <c r="C47">
-        <v>5549.785249776404</v>
+        <v>5464.962779017906</v>
       </c>
       <c r="D47">
-        <v>7301.060249776404</v>
+        <v>7310.052779017905</v>
       </c>
       <c r="E47">
-        <v>4035.475</v>
+        <v>4129.29</v>
       </c>
       <c r="F47">
-        <v>4221.675</v>
+        <v>4315.49</v>
       </c>
       <c r="G47">
         <v>2470.4</v>
@@ -5141,28 +5141,28 @@
         <v>1333.8</v>
       </c>
       <c r="M47">
-        <v>225.8596125</v>
+        <v>230.878715</v>
       </c>
       <c r="N47">
-        <v>1107.9403875</v>
+        <v>1102.921285</v>
       </c>
       <c r="O47">
-        <v>177.270462</v>
+        <v>176.4674056</v>
       </c>
       <c r="P47">
-        <v>930.6699255000002</v>
+        <v>926.4538794000001</v>
       </c>
       <c r="Q47">
-        <v>1711.2699255</v>
+        <v>1707.0538794</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1603968539810532</v>
+        <v>0.1623177782575555</v>
       </c>
       <c r="T47">
-        <v>1.57746882987605</v>
+        <v>1.603911075587574</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.905438273077708</v>
+        <v>5.777059180184714</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.10832400025908</v>
+        <v>0.1082067308285807</v>
       </c>
       <c r="C48">
-        <v>5464.962779017906</v>
+        <v>5380.162487313482</v>
       </c>
       <c r="D48">
-        <v>7310.052779017905</v>
+        <v>7319.067487313482</v>
       </c>
       <c r="E48">
-        <v>4129.29</v>
+        <v>4223.105</v>
       </c>
       <c r="F48">
-        <v>4315.49</v>
+        <v>4409.305</v>
       </c>
       <c r="G48">
         <v>2470.4</v>
@@ -5223,28 +5223,28 @@
         <v>1333.8</v>
       </c>
       <c r="M48">
-        <v>230.878715</v>
+        <v>235.8978175</v>
       </c>
       <c r="N48">
-        <v>1102.921285</v>
+        <v>1097.9021825</v>
       </c>
       <c r="O48">
-        <v>176.4674056</v>
+        <v>175.6643492</v>
       </c>
       <c r="P48">
-        <v>926.4538794000001</v>
+        <v>922.2378333000001</v>
       </c>
       <c r="Q48">
-        <v>1707.0538794</v>
+        <v>1702.8378333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1623177782575555</v>
+        <v>0.1643111902426051</v>
       </c>
       <c r="T48">
-        <v>1.603911075587574</v>
+        <v>1.631351141891985</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.777059180184714</v>
+        <v>5.654143027414826</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1082067308285807</v>
+        <v>0.1084120213980815</v>
       </c>
       <c r="C49">
-        <v>5380.162487313482</v>
+        <v>5270.581014369202</v>
       </c>
       <c r="D49">
-        <v>7319.067487313482</v>
+        <v>7303.301014369202</v>
       </c>
       <c r="E49">
-        <v>4223.105</v>
+        <v>4316.920000000001</v>
       </c>
       <c r="F49">
-        <v>4409.305</v>
+        <v>4503.120000000001</v>
       </c>
       <c r="G49">
         <v>2470.4</v>
@@ -5305,45 +5305,45 @@
         <v>1333.8</v>
       </c>
       <c r="M49">
-        <v>235.8978175</v>
+        <v>244.519416</v>
       </c>
       <c r="N49">
-        <v>1097.9021825</v>
+        <v>1089.280584</v>
       </c>
       <c r="O49">
-        <v>175.6643492</v>
+        <v>174.28489344</v>
       </c>
       <c r="P49">
-        <v>922.2378333000001</v>
+        <v>914.9956905600001</v>
       </c>
       <c r="Q49">
-        <v>1702.8378333</v>
+        <v>1695.59569056</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1643111902426051</v>
+        <v>0.1663812719193874</v>
       </c>
       <c r="T49">
-        <v>1.631351141891985</v>
+        <v>1.659846595361951</v>
       </c>
       <c r="U49">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V49">
         <v>0.16</v>
       </c>
       <c r="W49">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>5.654143027414826</v>
+        <v>5.454781554034138</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1084120213980815</v>
+        <v>0.1083014719675822</v>
       </c>
       <c r="C50">
-        <v>5270.581014369202</v>
+        <v>5185.247844940644</v>
       </c>
       <c r="D50">
-        <v>7303.301014369202</v>
+        <v>7311.782844940644</v>
       </c>
       <c r="E50">
-        <v>4316.92</v>
+        <v>4410.735</v>
       </c>
       <c r="F50">
-        <v>4503.12</v>
+        <v>4596.934999999999</v>
       </c>
       <c r="G50">
         <v>2470.4</v>
@@ -5387,28 +5387,28 @@
         <v>1333.8</v>
       </c>
       <c r="M50">
-        <v>244.519416</v>
+        <v>249.6135705</v>
       </c>
       <c r="N50">
-        <v>1089.280584</v>
+        <v>1084.1864295</v>
       </c>
       <c r="O50">
-        <v>174.28489344</v>
+        <v>173.46982872</v>
       </c>
       <c r="P50">
-        <v>914.9956905600001</v>
+        <v>910.7166007800002</v>
       </c>
       <c r="Q50">
-        <v>1695.59569056</v>
+        <v>1691.31660078</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1663812719193874</v>
+        <v>0.168532533269769</v>
       </c>
       <c r="T50">
-        <v>1.659846595361951</v>
+        <v>1.689459517595445</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.454781554034139</v>
+        <v>5.343459481502831</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1083014719675822</v>
+        <v>0.1081909225370829</v>
       </c>
       <c r="C51">
-        <v>5185.247844940644</v>
+        <v>5099.934399496477</v>
       </c>
       <c r="D51">
-        <v>7311.782844940644</v>
+        <v>7320.284399496476</v>
       </c>
       <c r="E51">
-        <v>4410.735</v>
+        <v>4504.55</v>
       </c>
       <c r="F51">
-        <v>4596.934999999999</v>
+        <v>4690.75</v>
       </c>
       <c r="G51">
         <v>2470.4</v>
@@ -5469,28 +5469,28 @@
         <v>1333.8</v>
       </c>
       <c r="M51">
-        <v>249.6135705</v>
+        <v>254.707725</v>
       </c>
       <c r="N51">
-        <v>1084.1864295</v>
+        <v>1079.092275</v>
       </c>
       <c r="O51">
-        <v>173.46982872</v>
+        <v>172.654764</v>
       </c>
       <c r="P51">
-        <v>910.7166007800002</v>
+        <v>906.4375110000002</v>
       </c>
       <c r="Q51">
-        <v>1691.31660078</v>
+        <v>1687.037511</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.168532533269769</v>
+        <v>0.1707698450741658</v>
       </c>
       <c r="T51">
-        <v>1.689459517595445</v>
+        <v>1.720256956718279</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.343459481502831</v>
+        <v>5.236590291872774</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1081909225370829</v>
+        <v>0.1080803731065836</v>
       </c>
       <c r="C52">
-        <v>5099.934399496477</v>
+        <v>5014.640746917181</v>
       </c>
       <c r="D52">
-        <v>7320.284399496476</v>
+        <v>7328.805746917181</v>
       </c>
       <c r="E52">
-        <v>4504.55</v>
+        <v>4598.365000000001</v>
       </c>
       <c r="F52">
-        <v>4690.75</v>
+        <v>4784.565000000001</v>
       </c>
       <c r="G52">
         <v>2470.4</v>
@@ -5551,28 +5551,28 @@
         <v>1333.8</v>
       </c>
       <c r="M52">
-        <v>254.707725</v>
+        <v>259.8018795</v>
       </c>
       <c r="N52">
-        <v>1079.092275</v>
+        <v>1073.9981205</v>
       </c>
       <c r="O52">
-        <v>172.654764</v>
+        <v>171.83969928</v>
       </c>
       <c r="P52">
-        <v>906.4375110000002</v>
+        <v>902.1584212200002</v>
       </c>
       <c r="Q52">
-        <v>1687.037511</v>
+        <v>1682.75842122</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1707698450741658</v>
+        <v>0.1730984757277217</v>
       </c>
       <c r="T52">
-        <v>1.720256956718279</v>
+        <v>1.752311434172657</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.236590291872774</v>
+        <v>5.13391205085566</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1080803731065836</v>
+        <v>0.1079698236760844</v>
       </c>
       <c r="C53">
-        <v>5014.640746917181</v>
+        <v>4929.366956404351</v>
       </c>
       <c r="D53">
-        <v>7328.805746917181</v>
+        <v>7337.346956404352</v>
       </c>
       <c r="E53">
-        <v>4598.365000000001</v>
+        <v>4692.18</v>
       </c>
       <c r="F53">
-        <v>4784.565000000001</v>
+        <v>4878.38</v>
       </c>
       <c r="G53">
         <v>2470.4</v>
@@ -5633,28 +5633,28 @@
         <v>1333.8</v>
       </c>
       <c r="M53">
-        <v>259.8018795</v>
+        <v>264.896034</v>
       </c>
       <c r="N53">
-        <v>1073.9981205</v>
+        <v>1068.903966</v>
       </c>
       <c r="O53">
-        <v>171.83969928</v>
+        <v>171.0246345600001</v>
       </c>
       <c r="P53">
-        <v>902.1584212200002</v>
+        <v>897.8793314400002</v>
       </c>
       <c r="Q53">
-        <v>1682.75842122</v>
+        <v>1678.47933144</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1730984757277217</v>
+        <v>0.1755241326585091</v>
       </c>
       <c r="T53">
-        <v>1.752311434172657</v>
+        <v>1.785701514854301</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.13391205085566</v>
+        <v>5.03518297295459</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1079698236760844</v>
+        <v>0.1078592742455851</v>
       </c>
       <c r="C54">
-        <v>4929.366956404351</v>
+        <v>4844.113097482556</v>
       </c>
       <c r="D54">
-        <v>7337.346956404352</v>
+        <v>7345.908097482557</v>
       </c>
       <c r="E54">
-        <v>4692.18</v>
+        <v>4785.995000000001</v>
       </c>
       <c r="F54">
-        <v>4878.38</v>
+        <v>4972.195000000001</v>
       </c>
       <c r="G54">
         <v>2470.4</v>
@@ -5715,28 +5715,28 @@
         <v>1333.8</v>
       </c>
       <c r="M54">
-        <v>264.896034</v>
+        <v>269.9901885</v>
       </c>
       <c r="N54">
-        <v>1068.903966</v>
+        <v>1063.8098115</v>
       </c>
       <c r="O54">
-        <v>171.0246345600001</v>
+        <v>170.2095698400001</v>
       </c>
       <c r="P54">
-        <v>897.8793314400002</v>
+        <v>893.6002416600002</v>
       </c>
       <c r="Q54">
-        <v>1678.47933144</v>
+        <v>1674.20024166</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1755241326585091</v>
+        <v>0.1780530090331597</v>
       </c>
       <c r="T54">
-        <v>1.785701514854301</v>
+        <v>1.820512450033035</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.03518297295459</v>
+        <v>4.940179520634691</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1078592742455851</v>
+        <v>0.1077487248150858</v>
       </c>
       <c r="C55">
-        <v>4844.113097482556</v>
+        <v>4758.879240001221</v>
       </c>
       <c r="D55">
-        <v>7345.908097482557</v>
+        <v>7354.48924000122</v>
       </c>
       <c r="E55">
-        <v>4785.995000000001</v>
+        <v>4879.81</v>
       </c>
       <c r="F55">
-        <v>4972.195000000001</v>
+        <v>5066.01</v>
       </c>
       <c r="G55">
         <v>2470.4</v>
@@ -5797,28 +5797,28 @@
         <v>1333.8</v>
       </c>
       <c r="M55">
-        <v>269.9901885</v>
+        <v>275.084343</v>
       </c>
       <c r="N55">
-        <v>1063.8098115</v>
+        <v>1058.715657</v>
       </c>
       <c r="O55">
-        <v>170.2095698400001</v>
+        <v>169.39450512</v>
       </c>
       <c r="P55">
-        <v>893.6002416600002</v>
+        <v>889.3211518800001</v>
       </c>
       <c r="Q55">
-        <v>1674.20024166</v>
+        <v>1669.92115188</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1780530090331597</v>
+        <v>0.1806918365545343</v>
       </c>
       <c r="T55">
-        <v>1.820512450033035</v>
+        <v>1.856836904132585</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.940179520634691</v>
+        <v>4.848694714697013</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1077487248150858</v>
+        <v>0.1076381753845865</v>
       </c>
       <c r="C56">
-        <v>4758.879240001221</v>
+        <v>4673.66545413653</v>
       </c>
       <c r="D56">
-        <v>7354.48924000122</v>
+        <v>7363.090454136531</v>
       </c>
       <c r="E56">
-        <v>4879.81</v>
+        <v>4973.625000000001</v>
       </c>
       <c r="F56">
-        <v>5066.01</v>
+        <v>5159.825000000001</v>
       </c>
       <c r="G56">
         <v>2470.4</v>
@@ -5879,28 +5879,28 @@
         <v>1333.8</v>
       </c>
       <c r="M56">
-        <v>275.084343</v>
+        <v>280.1784975</v>
       </c>
       <c r="N56">
-        <v>1058.715657</v>
+        <v>1053.6215025</v>
       </c>
       <c r="O56">
-        <v>169.39450512</v>
+        <v>168.5794404</v>
       </c>
       <c r="P56">
-        <v>889.3211518800001</v>
+        <v>885.0420621000001</v>
       </c>
       <c r="Q56">
-        <v>1669.92115188</v>
+        <v>1665.6420621</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1806918365545343</v>
+        <v>0.1834479452990812</v>
       </c>
       <c r="T56">
-        <v>1.856836904132585</v>
+        <v>1.894775778414336</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.848694714697013</v>
+        <v>4.760536628975248</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1076381753845865</v>
+        <v>0.1075276259540873</v>
       </c>
       <c r="C57">
-        <v>4673.66545413653</v>
+        <v>4588.471810393347</v>
       </c>
       <c r="D57">
-        <v>7363.090454136531</v>
+        <v>7371.711810393348</v>
       </c>
       <c r="E57">
-        <v>4973.625000000001</v>
+        <v>5067.440000000001</v>
       </c>
       <c r="F57">
-        <v>5159.825000000001</v>
+        <v>5253.64</v>
       </c>
       <c r="G57">
         <v>2470.4</v>
@@ -5961,28 +5961,28 @@
         <v>1333.8</v>
       </c>
       <c r="M57">
-        <v>280.1784975</v>
+        <v>285.2726520000001</v>
       </c>
       <c r="N57">
-        <v>1053.6215025</v>
+        <v>1048.527348</v>
       </c>
       <c r="O57">
-        <v>168.5794404</v>
+        <v>167.76437568</v>
       </c>
       <c r="P57">
-        <v>885.0420621000001</v>
+        <v>880.76297232</v>
       </c>
       <c r="Q57">
-        <v>1665.6420621</v>
+        <v>1661.36297232</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1834479452990812</v>
+        <v>0.1863293317138347</v>
       </c>
       <c r="T57">
-        <v>1.894775778414336</v>
+        <v>1.934439146981622</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.760536628975248</v>
+        <v>4.675527046314976</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1075276259540873</v>
+        <v>0.107417076523588</v>
       </c>
       <c r="C58">
-        <v>4588.471810393347</v>
+        <v>4503.298379607138</v>
       </c>
       <c r="D58">
-        <v>7371.711810393348</v>
+        <v>7380.353379607138</v>
       </c>
       <c r="E58">
-        <v>5067.440000000001</v>
+        <v>5161.255000000001</v>
       </c>
       <c r="F58">
-        <v>5253.64</v>
+        <v>5347.455000000001</v>
       </c>
       <c r="G58">
         <v>2470.4</v>
@@ -6043,28 +6043,28 @@
         <v>1333.8</v>
       </c>
       <c r="M58">
-        <v>285.2726520000001</v>
+        <v>290.3668065000001</v>
       </c>
       <c r="N58">
-        <v>1048.527348</v>
+        <v>1043.4331935</v>
       </c>
       <c r="O58">
-        <v>167.76437568</v>
+        <v>166.94931096</v>
       </c>
       <c r="P58">
-        <v>880.76297232</v>
+        <v>876.48388254</v>
       </c>
       <c r="Q58">
-        <v>1661.36297232</v>
+        <v>1657.08388254</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1863293317138347</v>
+        <v>0.1893447361013674</v>
       </c>
       <c r="T58">
-        <v>1.934439146981622</v>
+        <v>1.975947323389247</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.675527046314976</v>
+        <v>4.593500256028747</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.107417076523588</v>
+        <v>0.1073065270930887</v>
       </c>
       <c r="C59">
-        <v>4503.298379607138</v>
+        <v>4418.145232945899</v>
       </c>
       <c r="D59">
-        <v>7380.353379607138</v>
+        <v>7389.0152329459</v>
       </c>
       <c r="E59">
-        <v>5161.255000000001</v>
+        <v>5255.070000000001</v>
       </c>
       <c r="F59">
-        <v>5347.455000000001</v>
+        <v>5441.27</v>
       </c>
       <c r="G59">
         <v>2470.4</v>
@@ -6125,28 +6125,28 @@
         <v>1333.8</v>
       </c>
       <c r="M59">
-        <v>290.3668065000001</v>
+        <v>295.4609610000001</v>
       </c>
       <c r="N59">
-        <v>1043.4331935</v>
+        <v>1038.339039</v>
       </c>
       <c r="O59">
-        <v>166.94931096</v>
+        <v>166.13424624</v>
       </c>
       <c r="P59">
-        <v>876.48388254</v>
+        <v>872.2047927600001</v>
       </c>
       <c r="Q59">
-        <v>1657.08388254</v>
+        <v>1652.80479276</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1893447361013674</v>
+        <v>0.1925037311740207</v>
       </c>
       <c r="T59">
-        <v>1.975947323389247</v>
+        <v>2.019432079625806</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.593500256028747</v>
+        <v>4.514301975752391</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1073065270930887</v>
+        <v>0.1071959776625894</v>
       </c>
       <c r="C60">
-        <v>4418.1452329459</v>
+        <v>4333.012441912128</v>
       </c>
       <c r="D60">
-        <v>7389.0152329459</v>
+        <v>7397.697441912129</v>
       </c>
       <c r="E60">
-        <v>5255.07</v>
+        <v>5348.885</v>
       </c>
       <c r="F60">
-        <v>5441.27</v>
+        <v>5535.085</v>
       </c>
       <c r="G60">
         <v>2470.4</v>
@@ -6207,28 +6207,28 @@
         <v>1333.8</v>
       </c>
       <c r="M60">
-        <v>295.460961</v>
+        <v>300.5551155</v>
       </c>
       <c r="N60">
-        <v>1038.339039</v>
+        <v>1033.2448845</v>
       </c>
       <c r="O60">
-        <v>166.13424624</v>
+        <v>165.31918152</v>
       </c>
       <c r="P60">
-        <v>872.2047927600001</v>
+        <v>867.9257029800001</v>
       </c>
       <c r="Q60">
-        <v>1652.80479276</v>
+        <v>1648.52570298</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1925037311740207</v>
+        <v>0.1958168235672913</v>
       </c>
       <c r="T60">
-        <v>2.019432079625805</v>
+        <v>2.06503804348366</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.514301975752391</v>
+        <v>4.437788382943028</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1071959776625894</v>
+        <v>0.1070854282320901</v>
       </c>
       <c r="C61">
-        <v>4333.012441912128</v>
+        <v>4247.900078344786</v>
       </c>
       <c r="D61">
-        <v>7397.697441912129</v>
+        <v>7406.400078344785</v>
       </c>
       <c r="E61">
-        <v>5348.885</v>
+        <v>5442.7</v>
       </c>
       <c r="F61">
-        <v>5535.085</v>
+        <v>5628.9</v>
       </c>
       <c r="G61">
         <v>2470.4</v>
@@ -6289,28 +6289,28 @@
         <v>1333.8</v>
       </c>
       <c r="M61">
-        <v>300.5551155</v>
+        <v>305.64927</v>
       </c>
       <c r="N61">
-        <v>1033.2448845</v>
+        <v>1028.15073</v>
       </c>
       <c r="O61">
-        <v>165.31918152</v>
+        <v>164.5041168</v>
       </c>
       <c r="P61">
-        <v>867.9257029800001</v>
+        <v>863.6466132000003</v>
       </c>
       <c r="Q61">
-        <v>1648.52570298</v>
+        <v>1644.2466132</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1958168235672913</v>
+        <v>0.1992955705802254</v>
       </c>
       <c r="T61">
-        <v>2.06503804348366</v>
+        <v>2.112924305534408</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.437788382943028</v>
+        <v>4.363825243227312</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1070854282320901</v>
+        <v>0.1069748788015909</v>
       </c>
       <c r="C62">
-        <v>4247.900078344786</v>
+        <v>4162.808214421269</v>
       </c>
       <c r="D62">
-        <v>7406.400078344785</v>
+        <v>7415.12321442127</v>
       </c>
       <c r="E62">
-        <v>5442.7</v>
+        <v>5536.515</v>
       </c>
       <c r="F62">
-        <v>5628.9</v>
+        <v>5722.715</v>
       </c>
       <c r="G62">
         <v>2470.4</v>
@@ -6371,28 +6371,28 @@
         <v>1333.8</v>
       </c>
       <c r="M62">
-        <v>305.64927</v>
+        <v>310.7434245</v>
       </c>
       <c r="N62">
-        <v>1028.15073</v>
+        <v>1023.0565755</v>
       </c>
       <c r="O62">
-        <v>164.5041168</v>
+        <v>163.68905208</v>
       </c>
       <c r="P62">
-        <v>863.6466132000003</v>
+        <v>859.3675234200002</v>
       </c>
       <c r="Q62">
-        <v>1644.2466132</v>
+        <v>1639.96752342</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1992955705802254</v>
+        <v>0.202952714875874</v>
       </c>
       <c r="T62">
-        <v>2.112924305534408</v>
+        <v>2.163266273331347</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.363825243227312</v>
+        <v>4.29228712448588</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1069748788015909</v>
+        <v>0.1073851293710916</v>
       </c>
       <c r="C63">
-        <v>4162.808214421269</v>
+        <v>4036.724440210849</v>
       </c>
       <c r="D63">
-        <v>7415.12321442127</v>
+        <v>7382.854440210849</v>
       </c>
       <c r="E63">
-        <v>5536.515</v>
+        <v>5630.33</v>
       </c>
       <c r="F63">
-        <v>5722.715</v>
+        <v>5816.53</v>
       </c>
       <c r="G63">
         <v>2470.4</v>
@@ -6453,45 +6453,45 @@
         <v>1333.8</v>
       </c>
       <c r="M63">
-        <v>310.7434245</v>
+        <v>321.654109</v>
       </c>
       <c r="N63">
-        <v>1023.0565755</v>
+        <v>1012.145891</v>
       </c>
       <c r="O63">
-        <v>163.68905208</v>
+        <v>161.94334256</v>
       </c>
       <c r="P63">
-        <v>859.3675234200002</v>
+        <v>850.2025484400001</v>
       </c>
       <c r="Q63">
-        <v>1639.96752342</v>
+        <v>1630.80254844</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.202952714875874</v>
+        <v>0.2068023404502411</v>
       </c>
       <c r="T63">
-        <v>2.163266273331347</v>
+        <v>2.216257818380758</v>
       </c>
       <c r="U63">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V63">
         <v>0.16</v>
       </c>
       <c r="W63">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.29228712448588</v>
+        <v>4.146690381623572</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1073851293710916</v>
+        <v>0.1072829799405923</v>
       </c>
       <c r="C64">
-        <v>4036.724440210849</v>
+        <v>3950.917844625455</v>
       </c>
       <c r="D64">
-        <v>7382.854440210849</v>
+        <v>7390.862844625455</v>
       </c>
       <c r="E64">
-        <v>5630.33</v>
+        <v>5724.145</v>
       </c>
       <c r="F64">
-        <v>5816.53</v>
+        <v>5910.345</v>
       </c>
       <c r="G64">
         <v>2470.4</v>
@@ -6535,28 +6535,28 @@
         <v>1333.8</v>
       </c>
       <c r="M64">
-        <v>321.654109</v>
+        <v>326.8420785</v>
       </c>
       <c r="N64">
-        <v>1012.145891</v>
+        <v>1006.9579215</v>
       </c>
       <c r="O64">
-        <v>161.94334256</v>
+        <v>161.11326744</v>
       </c>
       <c r="P64">
-        <v>850.2025484400001</v>
+        <v>845.84465406</v>
       </c>
       <c r="Q64">
-        <v>1630.80254844</v>
+        <v>1626.44465406</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2068023404502411</v>
+        <v>0.2108600538934928</v>
       </c>
       <c r="T64">
-        <v>2.216257818380758</v>
+        <v>2.272113771270676</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.146690381623572</v>
+        <v>4.080869899375578</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1072829799405923</v>
+        <v>0.107180830510093</v>
       </c>
       <c r="C65">
-        <v>3950.917844625455</v>
+        <v>3865.128641821135</v>
       </c>
       <c r="D65">
-        <v>7390.862844625455</v>
+        <v>7398.888641821134</v>
       </c>
       <c r="E65">
-        <v>5724.145</v>
+        <v>5817.96</v>
       </c>
       <c r="F65">
-        <v>5910.345</v>
+        <v>6004.16</v>
       </c>
       <c r="G65">
         <v>2470.4</v>
@@ -6617,28 +6617,28 @@
         <v>1333.8</v>
       </c>
       <c r="M65">
-        <v>326.8420785</v>
+        <v>332.030048</v>
       </c>
       <c r="N65">
-        <v>1006.9579215</v>
+        <v>1001.769952</v>
       </c>
       <c r="O65">
-        <v>161.11326744</v>
+        <v>160.28319232</v>
       </c>
       <c r="P65">
-        <v>845.84465406</v>
+        <v>841.4867596800001</v>
       </c>
       <c r="Q65">
-        <v>1626.44465406</v>
+        <v>1622.08675968</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2108600538934928</v>
+        <v>0.2151431958613696</v>
       </c>
       <c r="T65">
-        <v>2.272113771270676</v>
+        <v>2.331072832654479</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.080869899375578</v>
+        <v>4.017106307197835</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.107180830510093</v>
+        <v>0.1070786810795938</v>
       </c>
       <c r="C66">
-        <v>3865.128641821135</v>
+        <v>3779.356888520357</v>
       </c>
       <c r="D66">
-        <v>7398.888641821134</v>
+        <v>7406.931888520357</v>
       </c>
       <c r="E66">
-        <v>5817.96</v>
+        <v>5911.775000000001</v>
       </c>
       <c r="F66">
-        <v>6004.16</v>
+        <v>6097.975</v>
       </c>
       <c r="G66">
         <v>2470.4</v>
@@ -6699,28 +6699,28 @@
         <v>1333.8</v>
       </c>
       <c r="M66">
-        <v>332.030048</v>
+        <v>337.2180175</v>
       </c>
       <c r="N66">
-        <v>1001.769952</v>
+        <v>996.5819825000001</v>
       </c>
       <c r="O66">
-        <v>160.28319232</v>
+        <v>159.4531172</v>
       </c>
       <c r="P66">
-        <v>841.4867596800001</v>
+        <v>837.1288653000001</v>
       </c>
       <c r="Q66">
-        <v>1622.08675968</v>
+        <v>1617.7288653</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2151431958613696</v>
+        <v>0.2196710887988394</v>
       </c>
       <c r="T66">
-        <v>2.331072832654479</v>
+        <v>2.393400983260214</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.017106307197835</v>
+        <v>3.955304671702484</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1070786810795938</v>
+        <v>0.1069765316490945</v>
       </c>
       <c r="C67">
-        <v>3779.356888520357</v>
+        <v>3693.602641692524</v>
       </c>
       <c r="D67">
-        <v>7406.931888520357</v>
+        <v>7414.992641692525</v>
       </c>
       <c r="E67">
-        <v>5911.775000000001</v>
+        <v>6005.59</v>
       </c>
       <c r="F67">
-        <v>6097.975</v>
+        <v>6191.79</v>
       </c>
       <c r="G67">
         <v>2470.4</v>
@@ -6781,28 +6781,28 @@
         <v>1333.8</v>
       </c>
       <c r="M67">
-        <v>337.2180175</v>
+        <v>342.405987</v>
       </c>
       <c r="N67">
-        <v>996.5819825000001</v>
+        <v>991.3940130000002</v>
       </c>
       <c r="O67">
-        <v>159.4531172</v>
+        <v>158.62304208</v>
       </c>
       <c r="P67">
-        <v>837.1288653000001</v>
+        <v>832.7709709200002</v>
       </c>
       <c r="Q67">
-        <v>1617.7288653</v>
+        <v>1613.37097092</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2196710887988394</v>
+        <v>0.2244653283796897</v>
       </c>
       <c r="T67">
-        <v>2.393400983260214</v>
+        <v>2.459395495666286</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.955304671702484</v>
+        <v>3.895375813040326</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1069765316490945</v>
+        <v>0.1068743822185952</v>
       </c>
       <c r="C68">
-        <v>3693.602641692524</v>
+        <v>3607.865958555291</v>
       </c>
       <c r="D68">
-        <v>7414.992641692525</v>
+        <v>7423.070958555292</v>
       </c>
       <c r="E68">
-        <v>6005.59</v>
+        <v>6099.405000000001</v>
       </c>
       <c r="F68">
-        <v>6191.79</v>
+        <v>6285.605</v>
       </c>
       <c r="G68">
         <v>2470.4</v>
@@ -6863,28 +6863,28 @@
         <v>1333.8</v>
       </c>
       <c r="M68">
-        <v>342.405987</v>
+        <v>347.5939565</v>
       </c>
       <c r="N68">
-        <v>991.3940130000002</v>
+        <v>986.2060435000001</v>
       </c>
       <c r="O68">
-        <v>158.62304208</v>
+        <v>157.79296696</v>
       </c>
       <c r="P68">
-        <v>832.7709709200002</v>
+        <v>828.41307654</v>
       </c>
       <c r="Q68">
-        <v>1613.37097092</v>
+        <v>1609.01307654</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2244653283796897</v>
+        <v>0.2295501279351371</v>
       </c>
       <c r="T68">
-        <v>2.459395495666286</v>
+        <v>2.529389675490909</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.895375813040326</v>
+        <v>3.837235875532261</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1068743822185952</v>
+        <v>0.1067722327880959</v>
       </c>
       <c r="C69">
-        <v>3607.865958555291</v>
+        <v>3522.146896575932</v>
       </c>
       <c r="D69">
-        <v>7423.070958555292</v>
+        <v>7431.166896575932</v>
       </c>
       <c r="E69">
-        <v>6099.405000000001</v>
+        <v>6193.22</v>
       </c>
       <c r="F69">
-        <v>6285.605</v>
+        <v>6379.42</v>
       </c>
       <c r="G69">
         <v>2470.4</v>
@@ -6945,28 +6945,28 @@
         <v>1333.8</v>
       </c>
       <c r="M69">
-        <v>347.5939565</v>
+        <v>352.781926</v>
       </c>
       <c r="N69">
-        <v>986.2060435000001</v>
+        <v>981.0180740000002</v>
       </c>
       <c r="O69">
-        <v>157.79296696</v>
+        <v>156.96289184</v>
       </c>
       <c r="P69">
-        <v>828.41307654</v>
+        <v>824.0551821600002</v>
       </c>
       <c r="Q69">
-        <v>1609.01307654</v>
+        <v>1604.65518216</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2295501279351371</v>
+        <v>0.2349527274627999</v>
       </c>
       <c r="T69">
-        <v>2.529389675490909</v>
+        <v>2.603758491554569</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.837235875532261</v>
+        <v>3.780805936186198</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1067722327880959</v>
+        <v>0.1066700833575967</v>
       </c>
       <c r="C70">
-        <v>3522.146896575932</v>
+        <v>3436.445513472698</v>
       </c>
       <c r="D70">
-        <v>7431.166896575932</v>
+        <v>7439.280513472699</v>
       </c>
       <c r="E70">
-        <v>6193.22</v>
+        <v>6287.035000000001</v>
       </c>
       <c r="F70">
-        <v>6379.42</v>
+        <v>6473.235000000001</v>
       </c>
       <c r="G70">
         <v>2470.4</v>
@@ -7027,28 +7027,28 @@
         <v>1333.8</v>
       </c>
       <c r="M70">
-        <v>352.781926</v>
+        <v>357.9698955000001</v>
       </c>
       <c r="N70">
-        <v>981.0180740000002</v>
+        <v>975.8301045000001</v>
       </c>
       <c r="O70">
-        <v>156.96289184</v>
+        <v>156.13281672</v>
       </c>
       <c r="P70">
-        <v>824.0551821600002</v>
+        <v>819.69728778</v>
       </c>
       <c r="Q70">
-        <v>1604.65518216</v>
+        <v>1600.29728778</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2349527274627999</v>
+        <v>0.240703881798699</v>
       </c>
       <c r="T70">
-        <v>2.603758491554569</v>
+        <v>2.682925295751369</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.780805936186198</v>
+        <v>3.726011647255963</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1066700833575967</v>
+        <v>0.1065679339270974</v>
       </c>
       <c r="C71">
-        <v>3436.445513472698</v>
+        <v>3350.761867216194</v>
       </c>
       <c r="D71">
-        <v>7439.280513472699</v>
+        <v>7447.411867216195</v>
       </c>
       <c r="E71">
-        <v>6287.035000000001</v>
+        <v>6380.85</v>
       </c>
       <c r="F71">
-        <v>6473.235000000001</v>
+        <v>6567.05</v>
       </c>
       <c r="G71">
         <v>2470.4</v>
@@ -7109,28 +7109,28 @@
         <v>1333.8</v>
       </c>
       <c r="M71">
-        <v>357.9698955000001</v>
+        <v>363.157865</v>
       </c>
       <c r="N71">
-        <v>975.8301045000001</v>
+        <v>970.6421350000002</v>
       </c>
       <c r="O71">
-        <v>156.13281672</v>
+        <v>155.3027416</v>
       </c>
       <c r="P71">
-        <v>819.69728778</v>
+        <v>815.3393934000002</v>
       </c>
       <c r="Q71">
-        <v>1600.29728778</v>
+        <v>1595.9393934</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.240703881798699</v>
+        <v>0.246838446423658</v>
       </c>
       <c r="T71">
-        <v>2.682925295751369</v>
+        <v>2.767369886894623</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.726011647255963</v>
+        <v>3.672782909438021</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1065679339270974</v>
+        <v>0.1064657844965981</v>
       </c>
       <c r="C72">
-        <v>3350.761867216194</v>
+        <v>3265.096016030758</v>
       </c>
       <c r="D72">
-        <v>7447.411867216195</v>
+        <v>7455.561016030758</v>
       </c>
       <c r="E72">
-        <v>6380.85</v>
+        <v>6474.665000000001</v>
       </c>
       <c r="F72">
-        <v>6567.05</v>
+        <v>6660.865000000001</v>
       </c>
       <c r="G72">
         <v>2470.4</v>
@@ -7191,28 +7191,28 @@
         <v>1333.8</v>
       </c>
       <c r="M72">
-        <v>363.157865</v>
+        <v>368.3458345</v>
       </c>
       <c r="N72">
-        <v>970.6421350000002</v>
+        <v>965.4541655000002</v>
       </c>
       <c r="O72">
-        <v>155.3027416</v>
+        <v>154.47266648</v>
       </c>
       <c r="P72">
-        <v>815.3393934000002</v>
+        <v>810.9814990200001</v>
       </c>
       <c r="Q72">
-        <v>1595.9393934</v>
+        <v>1591.58149902</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.246838446423658</v>
+        <v>0.2533960844710281</v>
       </c>
       <c r="T72">
-        <v>2.767369886894623</v>
+        <v>2.857638242944308</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.672782909438021</v>
+        <v>3.621053572685373</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1064657844965981</v>
+        <v>0.1063636350660989</v>
       </c>
       <c r="C73">
-        <v>3265.096016030759</v>
+        <v>3179.448018395847</v>
       </c>
       <c r="D73">
-        <v>7455.561016030758</v>
+        <v>7463.728018395846</v>
       </c>
       <c r="E73">
-        <v>6474.665</v>
+        <v>6568.48</v>
       </c>
       <c r="F73">
-        <v>6660.865</v>
+        <v>6754.679999999999</v>
       </c>
       <c r="G73">
         <v>2470.4</v>
@@ -7273,28 +7273,28 @@
         <v>1333.8</v>
       </c>
       <c r="M73">
-        <v>368.3458345</v>
+        <v>373.533804</v>
       </c>
       <c r="N73">
-        <v>965.4541655000002</v>
+        <v>960.2661960000003</v>
       </c>
       <c r="O73">
-        <v>154.47266648</v>
+        <v>153.64259136</v>
       </c>
       <c r="P73">
-        <v>810.9814990200001</v>
+        <v>806.6236046400002</v>
       </c>
       <c r="Q73">
-        <v>1591.58149902</v>
+        <v>1587.22360464</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.253396084471028</v>
+        <v>0.2604221252360673</v>
       </c>
       <c r="T73">
-        <v>2.857638242944307</v>
+        <v>2.954354338711827</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.621053572685373</v>
+        <v>3.570761161953632</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1063636350660989</v>
+        <v>0.1062614856355996</v>
       </c>
       <c r="C74">
-        <v>3179.448018395847</v>
+        <v>3093.817933047437</v>
       </c>
       <c r="D74">
-        <v>7463.728018395846</v>
+        <v>7471.912933047436</v>
       </c>
       <c r="E74">
-        <v>6568.48</v>
+        <v>6662.295</v>
       </c>
       <c r="F74">
-        <v>6754.679999999999</v>
+        <v>6848.495</v>
       </c>
       <c r="G74">
         <v>2470.4</v>
@@ -7355,28 +7355,28 @@
         <v>1333.8</v>
       </c>
       <c r="M74">
-        <v>373.533804</v>
+        <v>378.7217735</v>
       </c>
       <c r="N74">
-        <v>960.2661960000003</v>
+        <v>955.0782265000003</v>
       </c>
       <c r="O74">
-        <v>153.64259136</v>
+        <v>152.81251624</v>
       </c>
       <c r="P74">
-        <v>806.6236046400002</v>
+        <v>802.2657102600002</v>
       </c>
       <c r="Q74">
-        <v>1587.22360464</v>
+        <v>1582.86571026</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2604221252360673</v>
+        <v>0.2679686134651836</v>
       </c>
       <c r="T74">
-        <v>2.954354338711827</v>
+        <v>3.058234589721384</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.570761161953632</v>
+        <v>3.521846625488514</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1062614856355996</v>
+        <v>0.1061593362051003</v>
       </c>
       <c r="C75">
-        <v>3093.817933047437</v>
+        <v>3008.205818979432</v>
       </c>
       <c r="D75">
-        <v>7471.912933047436</v>
+        <v>7480.115818979431</v>
       </c>
       <c r="E75">
-        <v>6662.295</v>
+        <v>6756.11</v>
       </c>
       <c r="F75">
-        <v>6848.495</v>
+        <v>6942.309999999999</v>
       </c>
       <c r="G75">
         <v>2470.4</v>
@@ -7437,28 +7437,28 @@
         <v>1333.8</v>
       </c>
       <c r="M75">
-        <v>378.7217735</v>
+        <v>383.909743</v>
       </c>
       <c r="N75">
-        <v>955.0782265000003</v>
+        <v>949.8902570000002</v>
       </c>
       <c r="O75">
-        <v>152.81251624</v>
+        <v>151.98244112</v>
       </c>
       <c r="P75">
-        <v>802.2657102600002</v>
+        <v>797.9078158800003</v>
       </c>
       <c r="Q75">
-        <v>1582.86571026</v>
+        <v>1578.50781588</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2679686134651836</v>
+        <v>0.2760956007888473</v>
       </c>
       <c r="T75">
-        <v>3.058234589721384</v>
+        <v>3.170105629270139</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.521846625488514</v>
+        <v>3.474254103522453</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1061593362051003</v>
+        <v>0.106057186774601</v>
       </c>
       <c r="C76">
-        <v>3008.205818979432</v>
+        <v>2922.611735445087</v>
       </c>
       <c r="D76">
-        <v>7480.115818979431</v>
+        <v>7488.336735445087</v>
       </c>
       <c r="E76">
-        <v>6756.11</v>
+        <v>6849.925</v>
       </c>
       <c r="F76">
-        <v>6942.309999999999</v>
+        <v>7036.125</v>
       </c>
       <c r="G76">
         <v>2470.4</v>
@@ -7519,28 +7519,28 @@
         <v>1333.8</v>
       </c>
       <c r="M76">
-        <v>383.909743</v>
+        <v>389.0977125</v>
       </c>
       <c r="N76">
-        <v>949.8902570000002</v>
+        <v>944.7022875000002</v>
       </c>
       <c r="O76">
-        <v>151.98244112</v>
+        <v>151.152366</v>
       </c>
       <c r="P76">
-        <v>797.9078158800003</v>
+        <v>793.5499215000002</v>
       </c>
       <c r="Q76">
-        <v>1578.50781588</v>
+        <v>1574.1499215</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2760956007888473</v>
+        <v>0.2848727470984041</v>
       </c>
       <c r="T76">
-        <v>3.170105629270139</v>
+        <v>3.290926351982794</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.474254103522453</v>
+        <v>3.427930715475487</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.106057186774601</v>
+        <v>0.1059550373441017</v>
       </c>
       <c r="C77">
-        <v>2922.611735445087</v>
+        <v>2837.035741958425</v>
       </c>
       <c r="D77">
-        <v>7488.336735445087</v>
+        <v>7496.575741958425</v>
       </c>
       <c r="E77">
-        <v>6849.925</v>
+        <v>6943.740000000001</v>
       </c>
       <c r="F77">
-        <v>7036.125</v>
+        <v>7129.940000000001</v>
       </c>
       <c r="G77">
         <v>2470.4</v>
@@ -7601,28 +7601,28 @@
         <v>1333.8</v>
       </c>
       <c r="M77">
-        <v>389.0977125</v>
+        <v>394.2856820000001</v>
       </c>
       <c r="N77">
-        <v>944.7022875000002</v>
+        <v>939.5143180000001</v>
       </c>
       <c r="O77">
-        <v>151.152366</v>
+        <v>150.32229088</v>
       </c>
       <c r="P77">
-        <v>793.5499215000002</v>
+        <v>789.1920271200001</v>
       </c>
       <c r="Q77">
-        <v>1574.1499215</v>
+        <v>1569.79202712</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2848727470984041</v>
+        <v>0.2943813222670907</v>
       </c>
       <c r="T77">
-        <v>3.290926351982794</v>
+        <v>3.421815468254838</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.427930715475487</v>
+        <v>3.382826363956072</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1059550373441017</v>
+        <v>0.1058528879136025</v>
       </c>
       <c r="C78">
-        <v>2837.035741958425</v>
+        <v>2751.47789829568</v>
       </c>
       <c r="D78">
-        <v>7496.575741958425</v>
+        <v>7504.83289829568</v>
       </c>
       <c r="E78">
-        <v>6943.740000000001</v>
+        <v>7037.555</v>
       </c>
       <c r="F78">
-        <v>7129.940000000001</v>
+        <v>7223.755</v>
       </c>
       <c r="G78">
         <v>2470.4</v>
@@ -7683,28 +7683,28 @@
         <v>1333.8</v>
       </c>
       <c r="M78">
-        <v>394.2856820000001</v>
+        <v>399.4736515</v>
       </c>
       <c r="N78">
-        <v>939.5143180000001</v>
+        <v>934.3263485000002</v>
       </c>
       <c r="O78">
-        <v>150.32229088</v>
+        <v>149.4922157600001</v>
       </c>
       <c r="P78">
-        <v>789.1920271200001</v>
+        <v>784.8341327400002</v>
       </c>
       <c r="Q78">
-        <v>1569.79202712</v>
+        <v>1565.43413274</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2943813222670907</v>
+        <v>0.3047167300591412</v>
       </c>
       <c r="T78">
-        <v>3.421815468254838</v>
+        <v>3.564086246811406</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.382826363956072</v>
+        <v>3.338893554034565</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1058528879136025</v>
+        <v>0.1057507384831032</v>
       </c>
       <c r="C79">
-        <v>2751.47789829568</v>
+        <v>2665.938264496736</v>
       </c>
       <c r="D79">
-        <v>7504.83289829568</v>
+        <v>7513.108264496736</v>
       </c>
       <c r="E79">
-        <v>7037.555</v>
+        <v>7131.370000000001</v>
       </c>
       <c r="F79">
-        <v>7223.755</v>
+        <v>7317.570000000001</v>
       </c>
       <c r="G79">
         <v>2470.4</v>
@@ -7765,28 +7765,28 @@
         <v>1333.8</v>
       </c>
       <c r="M79">
-        <v>399.4736515</v>
+        <v>404.661621</v>
       </c>
       <c r="N79">
-        <v>934.3263485000002</v>
+        <v>929.1383790000002</v>
       </c>
       <c r="O79">
-        <v>149.4922157600001</v>
+        <v>148.66214064</v>
       </c>
       <c r="P79">
-        <v>784.8341327400002</v>
+        <v>780.4762383600001</v>
       </c>
       <c r="Q79">
-        <v>1565.43413274</v>
+        <v>1561.07623836</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3047167300591412</v>
+        <v>0.3159917203777419</v>
       </c>
       <c r="T79">
-        <v>3.564086246811406</v>
+        <v>3.719290732509481</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.338893554034565</v>
+        <v>3.296087226418737</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1057507384831032</v>
+        <v>0.1056485890526039</v>
       </c>
       <c r="C80">
-        <v>2665.938264496736</v>
+        <v>2580.416900866592</v>
       </c>
       <c r="D80">
-        <v>7513.108264496736</v>
+        <v>7521.401900866593</v>
       </c>
       <c r="E80">
-        <v>7131.370000000001</v>
+        <v>7225.185</v>
       </c>
       <c r="F80">
-        <v>7317.570000000001</v>
+        <v>7411.385</v>
       </c>
       <c r="G80">
         <v>2470.4</v>
@@ -7847,28 +7847,28 @@
         <v>1333.8</v>
       </c>
       <c r="M80">
-        <v>404.661621</v>
+        <v>409.8495905</v>
       </c>
       <c r="N80">
-        <v>929.1383790000002</v>
+        <v>923.9504095000002</v>
       </c>
       <c r="O80">
-        <v>148.66214064</v>
+        <v>147.83206552</v>
       </c>
       <c r="P80">
-        <v>780.4762383600001</v>
+        <v>776.1183439800002</v>
       </c>
       <c r="Q80">
-        <v>1561.07623836</v>
+        <v>1556.71834398</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3159917203777419</v>
+        <v>0.328340519298114</v>
       </c>
       <c r="T80">
-        <v>3.719290732509481</v>
+        <v>3.889276597797848</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.296087226418737</v>
+        <v>3.254364603299512</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1056485890526039</v>
+        <v>0.1055464396221047</v>
       </c>
       <c r="C81">
-        <v>2580.416900866592</v>
+        <v>2494.913867976817</v>
       </c>
       <c r="D81">
-        <v>7521.401900866593</v>
+        <v>7529.713867976818</v>
       </c>
       <c r="E81">
-        <v>7225.185</v>
+        <v>7319.000000000001</v>
       </c>
       <c r="F81">
-        <v>7411.385</v>
+        <v>7505.200000000001</v>
       </c>
       <c r="G81">
         <v>2470.4</v>
@@ -7929,28 +7929,28 @@
         <v>1333.8</v>
       </c>
       <c r="M81">
-        <v>409.8495905</v>
+        <v>415.03756</v>
       </c>
       <c r="N81">
-        <v>923.9504095000002</v>
+        <v>918.7624400000002</v>
       </c>
       <c r="O81">
-        <v>147.83206552</v>
+        <v>147.0019904</v>
       </c>
       <c r="P81">
-        <v>776.1183439800002</v>
+        <v>771.7604496000001</v>
       </c>
       <c r="Q81">
-        <v>1556.71834398</v>
+        <v>1552.3604496</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.328340519298114</v>
+        <v>0.3419241981105234</v>
       </c>
       <c r="T81">
-        <v>3.889276597797848</v>
+        <v>4.076261049615053</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.254364603299512</v>
+        <v>3.213685045758269</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1055464396221047</v>
+        <v>0.1054442901916054</v>
       </c>
       <c r="C82">
-        <v>2494.913867976817</v>
+        <v>2409.429226667034</v>
       </c>
       <c r="D82">
-        <v>7529.713867976818</v>
+        <v>7538.044226667033</v>
       </c>
       <c r="E82">
-        <v>7319.000000000001</v>
+        <v>7412.815000000001</v>
       </c>
       <c r="F82">
-        <v>7505.200000000001</v>
+        <v>7599.015</v>
       </c>
       <c r="G82">
         <v>2470.4</v>
@@ -8011,28 +8011,28 @@
         <v>1333.8</v>
       </c>
       <c r="M82">
-        <v>415.03756</v>
+        <v>420.2255295000001</v>
       </c>
       <c r="N82">
-        <v>918.7624400000002</v>
+        <v>913.5744705000002</v>
       </c>
       <c r="O82">
-        <v>147.0019904</v>
+        <v>146.17191528</v>
       </c>
       <c r="P82">
-        <v>771.7604496000001</v>
+        <v>767.4025552200002</v>
       </c>
       <c r="Q82">
-        <v>1552.3604496</v>
+        <v>1548.00255522</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3419241981105234</v>
+        <v>0.3569377378505548</v>
       </c>
       <c r="T82">
-        <v>4.076261049615053</v>
+        <v>4.282928075307753</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.213685045758269</v>
+        <v>3.174009921736562</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1054442901916054</v>
+        <v>0.1053421407611061</v>
       </c>
       <c r="C83">
-        <v>2409.429226667034</v>
+        <v>2323.963038046392</v>
       </c>
       <c r="D83">
-        <v>7538.044226667033</v>
+        <v>7546.393038046393</v>
       </c>
       <c r="E83">
-        <v>7412.815000000001</v>
+        <v>7506.630000000001</v>
       </c>
       <c r="F83">
-        <v>7599.015</v>
+        <v>7692.830000000001</v>
       </c>
       <c r="G83">
         <v>2470.4</v>
@@ -8093,28 +8093,28 @@
         <v>1333.8</v>
       </c>
       <c r="M83">
-        <v>420.2255295000001</v>
+        <v>425.4134990000001</v>
       </c>
       <c r="N83">
-        <v>913.5744705000002</v>
+        <v>908.3865010000002</v>
       </c>
       <c r="O83">
-        <v>146.17191528</v>
+        <v>145.34184016</v>
       </c>
       <c r="P83">
-        <v>767.4025552200002</v>
+        <v>763.0446608400001</v>
       </c>
       <c r="Q83">
-        <v>1548.00255522</v>
+        <v>1543.64466084</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3569377378505548</v>
+        <v>0.3736194486728118</v>
       </c>
       <c r="T83">
-        <v>4.282928075307753</v>
+        <v>4.512558103855197</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.174009921736562</v>
+        <v>3.135302483666603</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1053421407611061</v>
+        <v>0.1052399913306068</v>
       </c>
       <c r="C84">
-        <v>2323.963038046392</v>
+        <v>2238.515363495071</v>
       </c>
       <c r="D84">
-        <v>7546.393038046393</v>
+        <v>7554.760363495071</v>
       </c>
       <c r="E84">
-        <v>7506.630000000001</v>
+        <v>7600.445000000001</v>
       </c>
       <c r="F84">
-        <v>7692.830000000001</v>
+        <v>7786.645</v>
       </c>
       <c r="G84">
         <v>2470.4</v>
@@ -8175,28 +8175,28 @@
         <v>1333.8</v>
       </c>
       <c r="M84">
-        <v>425.4134990000001</v>
+        <v>430.6014685000001</v>
       </c>
       <c r="N84">
-        <v>908.3865010000002</v>
+        <v>903.1985315000002</v>
       </c>
       <c r="O84">
-        <v>145.34184016</v>
+        <v>144.51176504</v>
       </c>
       <c r="P84">
-        <v>763.0446608400001</v>
+        <v>758.6867664600002</v>
       </c>
       <c r="Q84">
-        <v>1543.64466084</v>
+        <v>1539.28676646</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3736194486728118</v>
+        <v>0.3922637137094521</v>
       </c>
       <c r="T84">
-        <v>4.512558103855197</v>
+        <v>4.769203429878811</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.135302483666603</v>
+        <v>3.097527754947729</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1052399913306068</v>
+        <v>0.1051378419001076</v>
       </c>
       <c r="C85">
-        <v>2238.515363495071</v>
+        <v>2153.086264665786</v>
       </c>
       <c r="D85">
-        <v>7554.760363495071</v>
+        <v>7563.146264665786</v>
       </c>
       <c r="E85">
-        <v>7600.445000000001</v>
+        <v>7694.260000000001</v>
       </c>
       <c r="F85">
-        <v>7786.645</v>
+        <v>7880.460000000001</v>
       </c>
       <c r="G85">
         <v>2470.4</v>
@@ -8257,28 +8257,28 @@
         <v>1333.8</v>
       </c>
       <c r="M85">
-        <v>430.6014685000001</v>
+        <v>435.7894380000001</v>
       </c>
       <c r="N85">
-        <v>903.1985315000002</v>
+        <v>898.0105620000002</v>
       </c>
       <c r="O85">
-        <v>144.51176504</v>
+        <v>143.68168992</v>
       </c>
       <c r="P85">
-        <v>758.6867664600002</v>
+        <v>754.3288720800001</v>
       </c>
       <c r="Q85">
-        <v>1539.28676646</v>
+        <v>1534.92887208</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3922637137094521</v>
+        <v>0.4132385118756725</v>
       </c>
       <c r="T85">
-        <v>4.769203429878811</v>
+        <v>5.057929421655377</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.097527754947729</v>
+        <v>3.060652424531684</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1051378419001076</v>
+        <v>0.1050356924696083</v>
       </c>
       <c r="C86">
-        <v>2153.086264665785</v>
+        <v>2067.675803485296</v>
       </c>
       <c r="D86">
-        <v>7563.146264665786</v>
+        <v>7571.550803485295</v>
       </c>
       <c r="E86">
-        <v>7694.26</v>
+        <v>7788.075</v>
       </c>
       <c r="F86">
-        <v>7880.46</v>
+        <v>7974.275</v>
       </c>
       <c r="G86">
         <v>2470.4</v>
@@ -8339,28 +8339,28 @@
         <v>1333.8</v>
       </c>
       <c r="M86">
-        <v>435.789438</v>
+        <v>440.9774075</v>
       </c>
       <c r="N86">
-        <v>898.0105620000002</v>
+        <v>892.8225925000002</v>
       </c>
       <c r="O86">
-        <v>143.68168992</v>
+        <v>142.8516148</v>
       </c>
       <c r="P86">
-        <v>754.3288720800001</v>
+        <v>749.9709777000002</v>
       </c>
       <c r="Q86">
-        <v>1534.92887208</v>
+        <v>1530.5709777</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4132385118756722</v>
+        <v>0.4370099497973885</v>
       </c>
       <c r="T86">
-        <v>5.057929421655373</v>
+        <v>5.38515221233548</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.060652424531684</v>
+        <v>3.024644748948959</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1050356924696083</v>
+        <v>0.106739543039109</v>
       </c>
       <c r="C87">
-        <v>2067.675803485296</v>
+        <v>1836.071481086055</v>
       </c>
       <c r="D87">
-        <v>7571.550803485295</v>
+        <v>7433.761481086056</v>
       </c>
       <c r="E87">
-        <v>7788.075</v>
+        <v>7881.89</v>
       </c>
       <c r="F87">
-        <v>7974.275</v>
+        <v>8068.09</v>
       </c>
       <c r="G87">
         <v>2470.4</v>
@@ -8421,45 +8421,45 @@
         <v>1333.8</v>
       </c>
       <c r="M87">
-        <v>440.9774075</v>
+        <v>466.3356020000001</v>
       </c>
       <c r="N87">
-        <v>892.8225925000002</v>
+        <v>867.4643980000001</v>
       </c>
       <c r="O87">
-        <v>142.8516148</v>
+        <v>138.79430368</v>
       </c>
       <c r="P87">
-        <v>749.9709777000002</v>
+        <v>728.6700943200001</v>
       </c>
       <c r="Q87">
-        <v>1530.5709777</v>
+        <v>1509.27009432</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4370099497973885</v>
+        <v>0.4641773074222071</v>
       </c>
       <c r="T87">
-        <v>5.38515221233548</v>
+        <v>5.759121115969889</v>
       </c>
       <c r="U87">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V87">
         <v>0.16</v>
       </c>
       <c r="W87">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.024644748948959</v>
+        <v>2.860171932573143</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.106739543039109</v>
+        <v>0.1066583936086097</v>
       </c>
       <c r="C88">
-        <v>1836.071481086055</v>
+        <v>1748.705147304968</v>
       </c>
       <c r="D88">
-        <v>7433.761481086056</v>
+        <v>7440.210147304967</v>
       </c>
       <c r="E88">
-        <v>7881.89</v>
+        <v>7975.705</v>
       </c>
       <c r="F88">
-        <v>8068.09</v>
+        <v>8161.905</v>
       </c>
       <c r="G88">
         <v>2470.4</v>
@@ -8503,28 +8503,28 @@
         <v>1333.8</v>
       </c>
       <c r="M88">
-        <v>466.3356020000001</v>
+        <v>471.758109</v>
       </c>
       <c r="N88">
-        <v>867.4643980000001</v>
+        <v>862.0418910000001</v>
       </c>
       <c r="O88">
-        <v>138.79430368</v>
+        <v>137.92670256</v>
       </c>
       <c r="P88">
-        <v>728.6700943200001</v>
+        <v>724.1151884400001</v>
       </c>
       <c r="Q88">
-        <v>1509.27009432</v>
+        <v>1504.71518844</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4641773074222071</v>
+        <v>0.4955242585277671</v>
       </c>
       <c r="T88">
-        <v>5.759121115969889</v>
+        <v>6.190623697086514</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.860171932573143</v>
+        <v>2.827296393118279</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1066583936086097</v>
+        <v>0.1065772441781105</v>
       </c>
       <c r="C89">
-        <v>1748.705147304968</v>
+        <v>1661.350011462366</v>
       </c>
       <c r="D89">
-        <v>7440.210147304967</v>
+        <v>7446.670011462365</v>
       </c>
       <c r="E89">
-        <v>7975.705</v>
+        <v>8069.52</v>
       </c>
       <c r="F89">
-        <v>8161.905</v>
+        <v>8255.719999999999</v>
       </c>
       <c r="G89">
         <v>2470.4</v>
@@ -8585,28 +8585,28 @@
         <v>1333.8</v>
       </c>
       <c r="M89">
-        <v>471.758109</v>
+        <v>477.180616</v>
       </c>
       <c r="N89">
-        <v>862.0418910000001</v>
+        <v>856.6193840000002</v>
       </c>
       <c r="O89">
-        <v>137.92670256</v>
+        <v>137.05910144</v>
       </c>
       <c r="P89">
-        <v>724.1151884400001</v>
+        <v>719.5602825600001</v>
       </c>
       <c r="Q89">
-        <v>1504.71518844</v>
+        <v>1500.16028256</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4955242585277671</v>
+        <v>0.5320957014842538</v>
       </c>
       <c r="T89">
-        <v>6.190623697086514</v>
+        <v>6.694043375055911</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.827296393118279</v>
+        <v>2.795168025014663</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1065772441781105</v>
+        <v>0.1064960947476112</v>
       </c>
       <c r="C90">
-        <v>1661.350011462366</v>
+        <v>1574.006102750978</v>
       </c>
       <c r="D90">
-        <v>7446.670011462365</v>
+        <v>7453.141102750978</v>
       </c>
       <c r="E90">
-        <v>8069.52</v>
+        <v>8163.335</v>
       </c>
       <c r="F90">
-        <v>8255.719999999999</v>
+        <v>8349.535</v>
       </c>
       <c r="G90">
         <v>2470.4</v>
@@ -8667,28 +8667,28 @@
         <v>1333.8</v>
       </c>
       <c r="M90">
-        <v>477.180616</v>
+        <v>482.603123</v>
       </c>
       <c r="N90">
-        <v>856.6193840000002</v>
+        <v>851.1968770000001</v>
       </c>
       <c r="O90">
-        <v>137.05910144</v>
+        <v>136.19150032</v>
       </c>
       <c r="P90">
-        <v>719.5602825600001</v>
+        <v>715.00537668</v>
       </c>
       <c r="Q90">
-        <v>1500.16028256</v>
+        <v>1495.60537668</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5320957014842538</v>
+        <v>0.5753164977055562</v>
       </c>
       <c r="T90">
-        <v>6.694043375055911</v>
+        <v>7.288993903565197</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.795168025014663</v>
+        <v>2.763761642711127</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1064960947476112</v>
+        <v>0.1064149453171119</v>
       </c>
       <c r="C91">
-        <v>1574.006102750978</v>
+        <v>1486.673450465099</v>
       </c>
       <c r="D91">
-        <v>7453.141102750978</v>
+        <v>7459.623450465099</v>
       </c>
       <c r="E91">
-        <v>8163.335</v>
+        <v>8257.15</v>
       </c>
       <c r="F91">
-        <v>8349.535</v>
+        <v>8443.35</v>
       </c>
       <c r="G91">
         <v>2470.4</v>
@@ -8749,28 +8749,28 @@
         <v>1333.8</v>
       </c>
       <c r="M91">
-        <v>482.603123</v>
+        <v>488.02563</v>
       </c>
       <c r="N91">
-        <v>851.1968770000001</v>
+        <v>845.7743700000001</v>
       </c>
       <c r="O91">
-        <v>136.19150032</v>
+        <v>135.3238992</v>
       </c>
       <c r="P91">
-        <v>715.00537668</v>
+        <v>710.4504708000001</v>
       </c>
       <c r="Q91">
-        <v>1495.60537668</v>
+        <v>1491.0504708</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5753164977055562</v>
+        <v>0.6271814531711192</v>
       </c>
       <c r="T91">
-        <v>7.288993903565197</v>
+        <v>8.002934537776342</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.763761642711127</v>
+        <v>2.733053180014337</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1064149453171119</v>
+        <v>0.1063337958866126</v>
       </c>
       <c r="C92">
-        <v>1486.673450465099</v>
+        <v>1399.352084001031</v>
       </c>
       <c r="D92">
-        <v>7459.623450465099</v>
+        <v>7466.117084001032</v>
       </c>
       <c r="E92">
-        <v>8257.15</v>
+        <v>8350.965</v>
       </c>
       <c r="F92">
-        <v>8443.35</v>
+        <v>8537.165000000001</v>
       </c>
       <c r="G92">
         <v>2470.4</v>
@@ -8831,28 +8831,28 @@
         <v>1333.8</v>
       </c>
       <c r="M92">
-        <v>488.02563</v>
+        <v>493.4481370000001</v>
       </c>
       <c r="N92">
-        <v>845.7743700000001</v>
+        <v>840.3518630000001</v>
       </c>
       <c r="O92">
-        <v>135.3238992</v>
+        <v>134.45629808</v>
       </c>
       <c r="P92">
-        <v>710.4504708000001</v>
+        <v>705.8955649200001</v>
       </c>
       <c r="Q92">
-        <v>1491.0504708</v>
+        <v>1486.49556492</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6271814531711192</v>
+        <v>0.6905719542956961</v>
       </c>
       <c r="T92">
-        <v>8.002934537776342</v>
+        <v>8.87552864625663</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.733053180014337</v>
+        <v>2.703019628585607</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1063337958866126</v>
+        <v>0.1062526464561134</v>
       </c>
       <c r="C93">
-        <v>1399.352084001031</v>
+        <v>1312.042032857515</v>
       </c>
       <c r="D93">
-        <v>7466.117084001032</v>
+        <v>7472.622032857515</v>
       </c>
       <c r="E93">
-        <v>8350.965</v>
+        <v>8444.779999999999</v>
       </c>
       <c r="F93">
-        <v>8537.165000000001</v>
+        <v>8630.98</v>
       </c>
       <c r="G93">
         <v>2470.4</v>
@@ -8913,28 +8913,28 @@
         <v>1333.8</v>
       </c>
       <c r="M93">
-        <v>493.4481370000001</v>
+        <v>498.870644</v>
       </c>
       <c r="N93">
-        <v>840.3518630000001</v>
+        <v>834.9293560000001</v>
       </c>
       <c r="O93">
-        <v>134.45629808</v>
+        <v>133.58869696</v>
       </c>
       <c r="P93">
-        <v>705.8955649200001</v>
+        <v>701.3406590400001</v>
       </c>
       <c r="Q93">
-        <v>1486.49556492</v>
+        <v>1481.94065904</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6905719542956961</v>
+        <v>0.7698100807014173</v>
       </c>
       <c r="T93">
-        <v>8.87552864625663</v>
+        <v>9.96627128185699</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.703019628585607</v>
+        <v>2.673638980448808</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1062526464561134</v>
+        <v>0.1061714970256141</v>
       </c>
       <c r="C94">
-        <v>1312.042032857515</v>
+        <v>1224.743326636191</v>
       </c>
       <c r="D94">
-        <v>7472.622032857515</v>
+        <v>7479.138326636191</v>
       </c>
       <c r="E94">
-        <v>8444.779999999999</v>
+        <v>8538.594999999999</v>
       </c>
       <c r="F94">
-        <v>8630.98</v>
+        <v>8724.795</v>
       </c>
       <c r="G94">
         <v>2470.4</v>
@@ -8995,28 +8995,28 @@
         <v>1333.8</v>
       </c>
       <c r="M94">
-        <v>498.870644</v>
+        <v>504.293151</v>
       </c>
       <c r="N94">
-        <v>834.9293560000001</v>
+        <v>829.5068490000001</v>
       </c>
       <c r="O94">
-        <v>133.58869696</v>
+        <v>132.72109584</v>
       </c>
       <c r="P94">
-        <v>701.3406590400001</v>
+        <v>696.78575316</v>
       </c>
       <c r="Q94">
-        <v>1481.94065904</v>
+        <v>1477.38575316</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7698100807014173</v>
+        <v>0.8716876717944874</v>
       </c>
       <c r="T94">
-        <v>9.96627128185699</v>
+        <v>11.36865467048602</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.673638980448808</v>
+        <v>2.644890174207423</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1061714970256141</v>
+        <v>0.1060903475951148</v>
       </c>
       <c r="C95">
-        <v>1224.743326636191</v>
+        <v>1137.455995042039</v>
       </c>
       <c r="D95">
-        <v>7479.138326636191</v>
+        <v>7485.665995042039</v>
       </c>
       <c r="E95">
-        <v>8538.594999999999</v>
+        <v>8632.41</v>
       </c>
       <c r="F95">
-        <v>8724.795</v>
+        <v>8818.610000000001</v>
       </c>
       <c r="G95">
         <v>2470.4</v>
@@ -9077,28 +9077,28 @@
         <v>1333.8</v>
       </c>
       <c r="M95">
-        <v>504.293151</v>
+        <v>509.7156580000001</v>
       </c>
       <c r="N95">
-        <v>829.5068490000001</v>
+        <v>824.0843420000001</v>
       </c>
       <c r="O95">
-        <v>132.72109584</v>
+        <v>131.85349472</v>
       </c>
       <c r="P95">
-        <v>696.78575316</v>
+        <v>692.23084728</v>
       </c>
       <c r="Q95">
-        <v>1477.38575316</v>
+        <v>1472.83084728</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8716876717944874</v>
+        <v>1.007524459918581</v>
       </c>
       <c r="T95">
-        <v>11.36865467048602</v>
+        <v>13.23849918865807</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.644890174207423</v>
+        <v>2.616753044694577</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1060903475951148</v>
+        <v>0.1060091981646155</v>
       </c>
       <c r="C96">
-        <v>1137.455995042039</v>
+        <v>1050.180067883837</v>
       </c>
       <c r="D96">
-        <v>7485.665995042039</v>
+        <v>7492.205067883838</v>
       </c>
       <c r="E96">
-        <v>8632.41</v>
+        <v>8726.225</v>
       </c>
       <c r="F96">
-        <v>8818.610000000001</v>
+        <v>8912.425000000001</v>
       </c>
       <c r="G96">
         <v>2470.4</v>
@@ -9159,28 +9159,28 @@
         <v>1333.8</v>
       </c>
       <c r="M96">
-        <v>509.7156580000001</v>
+        <v>515.1381650000001</v>
       </c>
       <c r="N96">
-        <v>824.0843420000001</v>
+        <v>818.6618350000001</v>
       </c>
       <c r="O96">
-        <v>131.85349472</v>
+        <v>130.9858936</v>
       </c>
       <c r="P96">
-        <v>692.23084728</v>
+        <v>687.6759414000001</v>
       </c>
       <c r="Q96">
-        <v>1472.83084728</v>
+        <v>1468.2759414</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.007524459918581</v>
+        <v>1.197695963292312</v>
       </c>
       <c r="T96">
-        <v>13.23849918865807</v>
+        <v>15.85628151409894</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.616753044694577</v>
+        <v>2.589208275803056</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1060091981646155</v>
+        <v>0.1059280487341163</v>
       </c>
       <c r="C97">
-        <v>1050.180067883837</v>
+        <v>962.9155750746122</v>
       </c>
       <c r="D97">
-        <v>7492.205067883838</v>
+        <v>7498.755575074613</v>
       </c>
       <c r="E97">
-        <v>8726.225</v>
+        <v>8820.040000000001</v>
       </c>
       <c r="F97">
-        <v>8912.425000000001</v>
+        <v>9006.240000000002</v>
       </c>
       <c r="G97">
         <v>2470.4</v>
@@ -9241,28 +9241,28 @@
         <v>1333.8</v>
       </c>
       <c r="M97">
-        <v>515.1381650000001</v>
+        <v>520.5606720000002</v>
       </c>
       <c r="N97">
-        <v>818.6618350000001</v>
+        <v>813.239328</v>
       </c>
       <c r="O97">
-        <v>130.9858936</v>
+        <v>130.11829248</v>
       </c>
       <c r="P97">
-        <v>687.6759414000001</v>
+        <v>683.12103552</v>
       </c>
       <c r="Q97">
-        <v>1468.2759414</v>
+        <v>1463.72103552</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.197695963292312</v>
+        <v>1.482953218352909</v>
       </c>
       <c r="T97">
-        <v>15.85628151409894</v>
+        <v>19.78295500226024</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.589208275803056</v>
+        <v>2.56223735626344</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1059280487341163</v>
+        <v>0.105846899303617</v>
       </c>
       <c r="C98">
-        <v>962.9155750746122</v>
+        <v>875.6625466320911</v>
       </c>
       <c r="D98">
-        <v>7498.755575074611</v>
+        <v>7505.317546632091</v>
       </c>
       <c r="E98">
-        <v>8820.039999999999</v>
+        <v>8913.855</v>
       </c>
       <c r="F98">
-        <v>9006.24</v>
+        <v>9100.055</v>
       </c>
       <c r="G98">
         <v>2470.4</v>
@@ -9323,28 +9323,28 @@
         <v>1333.8</v>
       </c>
       <c r="M98">
-        <v>520.5606720000001</v>
+        <v>525.9831790000001</v>
       </c>
       <c r="N98">
-        <v>813.2393280000001</v>
+        <v>807.8168210000001</v>
       </c>
       <c r="O98">
-        <v>130.11829248</v>
+        <v>129.25069136</v>
       </c>
       <c r="P98">
-        <v>683.1210355200001</v>
+        <v>678.5661296400001</v>
       </c>
       <c r="Q98">
-        <v>1463.72103552</v>
+        <v>1459.16612964</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.482953218352906</v>
+        <v>1.958381976787232</v>
       </c>
       <c r="T98">
-        <v>19.78295500226019</v>
+        <v>26.32741081586234</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.562237356263441</v>
+        <v>2.535822538157632</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.105846899303617</v>
+        <v>0.1057657498731177</v>
       </c>
       <c r="C99">
-        <v>875.6625466320911</v>
+        <v>788.4210126791713</v>
       </c>
       <c r="D99">
-        <v>7505.317546632091</v>
+        <v>7511.891012679171</v>
       </c>
       <c r="E99">
-        <v>8913.855</v>
+        <v>9007.669999999998</v>
       </c>
       <c r="F99">
-        <v>9100.055</v>
+        <v>9193.869999999999</v>
       </c>
       <c r="G99">
         <v>2470.4</v>
@@ -9405,28 +9405,28 @@
         <v>1333.8</v>
       </c>
       <c r="M99">
-        <v>525.9831790000001</v>
+        <v>531.4056859999999</v>
       </c>
       <c r="N99">
-        <v>807.8168210000001</v>
+        <v>802.3943140000002</v>
       </c>
       <c r="O99">
-        <v>129.25069136</v>
+        <v>128.38309024</v>
       </c>
       <c r="P99">
-        <v>678.5661296400001</v>
+        <v>674.0112237600002</v>
       </c>
       <c r="Q99">
-        <v>1459.16612964</v>
+        <v>1454.61122376</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.958381976787232</v>
+        <v>2.909239493655883</v>
       </c>
       <c r="T99">
-        <v>26.32741081586234</v>
+        <v>39.41632244306661</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.535822538157632</v>
+        <v>2.509946797972351</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1057657498731177</v>
+        <v>0.1085952004426184</v>
       </c>
       <c r="C100">
-        <v>788.4210126791713</v>
+        <v>472.0049601260489</v>
       </c>
       <c r="D100">
-        <v>7511.891012679171</v>
+        <v>7289.289960126048</v>
       </c>
       <c r="E100">
-        <v>9007.669999999998</v>
+        <v>9101.484999999999</v>
       </c>
       <c r="F100">
-        <v>9193.869999999999</v>
+        <v>9287.684999999999</v>
       </c>
       <c r="G100">
         <v>2470.4</v>
@@ -9487,129 +9487,47 @@
         <v>1333.8</v>
       </c>
       <c r="M100">
-        <v>531.4056859999999</v>
+        <v>569.3350905</v>
       </c>
       <c r="N100">
-        <v>802.3943140000002</v>
+        <v>764.4649095000002</v>
       </c>
       <c r="O100">
-        <v>128.38309024</v>
+        <v>122.31438552</v>
       </c>
       <c r="P100">
-        <v>674.0112237600002</v>
+        <v>642.1505239800001</v>
       </c>
       <c r="Q100">
-        <v>1454.61122376</v>
+        <v>1422.75052398</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.909239493655883</v>
+        <v>5.761812044261839</v>
       </c>
       <c r="T100">
-        <v>39.41632244306661</v>
+        <v>78.68305732467947</v>
       </c>
       <c r="U100">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V100">
         <v>0.16</v>
       </c>
       <c r="W100">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.509946797972351</v>
+        <v>2.342732816325503</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1085952004426184</v>
-      </c>
-      <c r="C101">
-        <v>472.0049601260489</v>
-      </c>
-      <c r="D101">
-        <v>7289.289960126048</v>
-      </c>
-      <c r="E101">
-        <v>9101.484999999999</v>
-      </c>
-      <c r="F101">
-        <v>9287.684999999999</v>
-      </c>
-      <c r="G101">
-        <v>2470.4</v>
-      </c>
-      <c r="H101">
-        <v>9195.299999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2114.4</v>
-      </c>
-      <c r="K101">
-        <v>780.6</v>
-      </c>
-      <c r="L101">
-        <v>1333.8</v>
-      </c>
-      <c r="M101">
-        <v>569.3350905</v>
-      </c>
-      <c r="N101">
-        <v>764.4649095000002</v>
-      </c>
-      <c r="O101">
-        <v>122.31438552</v>
-      </c>
-      <c r="P101">
-        <v>642.1505239800001</v>
-      </c>
-      <c r="Q101">
-        <v>1422.75052398</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.761812044261839</v>
-      </c>
-      <c r="T101">
-        <v>78.68305732467947</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.16</v>
-      </c>
-      <c r="W101">
-        <v>0.051492</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.342732816325503</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
